--- a/deliverables/Berka_Summary_Workbook.xlsx
+++ b/deliverables/Berka_Summary_Workbook.xlsx
@@ -16,7 +16,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'1 Defects'!$A$1:$J$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'6 Design decisions'!$A$4:$F$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'6 Design decisions'!$A$4:$F$33</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -25,7 +25,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -54,6 +54,10 @@
     <font>
       <name val="Consolas"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="12"/>
     </font>
   </fonts>
   <fills count="8">
@@ -120,7 +124,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -157,6 +161,7 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -645,7 +650,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Closing balance of the account's last day is not uniquely determined</t>
+          <t>Account has several postings on its latest date (closing posting must be derived)</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -670,7 +675,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>trans_id is not chronological within a date, so when an account has several postings on one day there is no way to tell which one closed the day. For 183 accounts that ambiguity falls on their most recent date, which is precisely the balance Q9 reports. The answer is therefore a documented choice (highest trans_id on the latest date) rather than a fact, and the count of affected accounts belongs next to the answer. Warn: the data is not wrong, the determinism is missing.</t>
+          <t>trans_id is not chronological within a date and the source has no time of day, so when an account has several postings on one day the closing one has to be derived. 183 accounts have this on their most recent date, which is the balance Q9 reports. The running balance resolves it (D028): each posting starts at balance_after - signed_amount, and the closing posting is the end of that chain. That settles 141 of the 183; for the other 42 the chain does not order the postings, the documented fallback is used and the month-end row is marked closing_basis = 'ambiguous'. Warn: the data is not wrong, the order has to be inferred.</t>
         </is>
       </c>
       <c r="G3" s="2" t="n">
@@ -678,7 +683,7 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>Tie-break documented in the semantic layer and applied identically in the reference SQL and in core.fact_account_month_end_balance; affected accounts flagged so the caveat can be quantified.</t>
+          <t>Closing posting taken from the running-balance chain in core.fact_account_month_end_balance (closing_basis records how); accounts flagged so the caveat can be quantified.</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
@@ -688,29 +693,29 @@
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>account has 2 postings on its latest date 1998-12-31; the closing balance depends on the tie-break</t>
+          <t>account has 2 postings on its latest date 1998-12-31; the closing posting is derived from the running-balance chain</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Running balance does not reconcile</t>
+          <t>Implausible age</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>trans</t>
+          <t>client, loan</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>CON_BALANCE_RECONCILIATION_MATERIAL, CON_BALANCE_RECONCILIATION_ROUNDING</t>
+          <t>VAL_OWNER_AGE_AT_ACCOUNT_OPEN, VAL_OWNER_AGE_AT_LOAN_START</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>consistency</t>
+          <t>validity</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
@@ -720,47 +725,47 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Tested order independently: the sum of all signed amounts on an account should equal its last reported balance, whatever order the postings are read in. 136 accounts breach a 1 CZK tolerance; 81 of those are within 100 CZK and sit in the rounding band (every amount in the source carries a single decimal, so residuals accumulate). Warn, because the account is still usable and the Q9 average moves by cents; the band is reported so nobody confuses it with the material tier below. | 55 accounts are off by more than 100 CZK and one by exactly 1,200.00 CZK with only 55 postings, which is a missing or extra posting rather than rounding. This is the single most material finding for Q9, because the answer is an average balance and these accounts' balances cannot be derived from their own flows. It stays warn rather than block on purpose: the balance column is what Q9 reads, and it is internally plausible -- it is the *flows* that disagree with it. Quarantining the accounts would remove real balances from an average; blocking the postings would break the chain further. The defensible treatment is to publish the answer with the affected population and the residual attached, which is what the semantic layer makes the LLM do.</t>
+          <t>114 owners were under 15 when their account was opened, the youngest 10.3 years. A ten year old cannot be the legal holder of a current account, so either the birth number or the owner flag is wrong. It is warn rather than block because the accounts and their transactions are otherwise well-formed and feed Q5, Q6 and Q9 correctly: quarantining 114 accounts to protect the age metric would damage four answers to improve one. Q7 and Q8 report their coverage instead. | 6 loans were granted to owners recorded as under 15. Q7 reports exactly this number -- the average age of the owner at loan start, per status -- so these rows pull the answer directly. Warn rather than block because the loan amount and status are themselves sound and feed Q2, Q3, Q4 and Q10: removing the loans would make the certified loan total disagree with the source. Q7 publishes the flagged count next to the average, which is the honest treatment of a value that is probably wrong but not certainly so.</t>
         </is>
       </c>
       <c r="G4" s="2" t="n">
-        <v>136</v>
+        <v>120</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Account flagged; the month-end balance fact carries the residual so a user can see the size of the discrepancy next to the balance. | Account flagged as balance_unreconciled; Q9 reports the average together with the number of affected accounts and the total residual, so the reader can size the uncertainty instead of guessing at it.</t>
+          <t>Rows kept and flagged (_dq_flags carries 'owner_age_implausible'); the semantic layer attaches the caveat to the age metric so the LLM can repeat it. | Rows kept and flagged; Q7 reports the average with and without the flagged loans so the sensitivity is visible.</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>Q9</t>
+          <t>Q7, Q8</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>sum(signed_amount) = 13298.70 but last reported balance = 13312.90 (difference -14.20)</t>
+          <t>owner was 11.9 years old when account 9 was opened</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Implausible age</t>
+          <t>Running balance does not reconcile</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>client, loan</t>
+          <t>trans</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>VAL_OWNER_AGE_AT_ACCOUNT_OPEN, VAL_OWNER_AGE_AT_LOAN_START</t>
+          <t>CON_BALANCE_RECONCILIATION_MATERIAL, CON_BALANCE_RECONCILIATION_ROUNDING</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>validity</t>
+          <t>consistency</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -770,25 +775,25 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>114 owners were under 15 when their account was opened, the youngest 10.3 years. A ten year old cannot be the legal holder of a current account, so either the birth number or the owner flag is wrong. It is warn rather than block because the accounts and their transactions are otherwise well-formed and feed Q5, Q6 and Q9 correctly: quarantining 114 accounts to protect the age metric would damage four answers to improve one. Q7 and Q8 report their coverage instead. | 6 loans were granted to owners recorded as under 15. Q7 reports exactly this number -- the average age of the owner at loan start, per status -- so these rows pull the answer directly. Warn rather than block because the loan amount and status are themselves sound and feed Q2, Q3, Q4 and Q10: removing the loans would make the certified loan total disagree with the source. Q7 publishes the flagged count next to the average, which is the honest treatment of a value that is probably wrong but not certainly so.</t>
+          <t>Tested order independently: the sum of all signed amounts on an account should equal its last reported balance, whatever order the postings are read in. The last reported balance is the end of the last day's running-balance chain (D028). 84 accounts breach a 1 CZK tolerance; 70 of those are within 100 CZK and sit in the rounding band (every amount in the source carries a single decimal, so residuals accumulate). The earlier highest-trans_id choice of "last balance" made 136 accounts appear to breach, 52 of them only because it read a mid-day balance. Warn, because the account is still usable and the Q9 average moves by cents; the band is reported so nobody confuses it with the material tier below. | 14 accounts are off by more than 100 CZK (largest 488.30 CZK, account 8856), which is a missing or extra posting rather than rounding. Before D028 the rule read a mid-day balance as the last one and reported 55, including an apparent 1,200 CZK break that was not real. This is the single most material finding for Q9, because the answer is an average balance and these accounts' balances cannot be derived from their own flows. It stays warn rather than block on purpose: the balance column is what Q9 reads, and it is internally plausible -- it is the *flows* that disagree with it. Quarantining the accounts would remove real balances from an average; blocking the postings would break the chain further. The defensible treatment is to publish the answer with the affected population and the residual attached, which is what the semantic layer makes the LLM do.</t>
         </is>
       </c>
       <c r="G5" s="2" t="n">
-        <v>120</v>
+        <v>84</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>Rows kept and flagged (_dq_flags carries 'owner_age_implausible'); the semantic layer attaches the caveat to the age metric so the LLM can repeat it. | Rows kept and flagged; Q7 reports the average with and without the flagged loans so the sensitivity is visible.</t>
+          <t>Account flagged; the month-end balance fact carries the residual so a user can see the size of the discrepancy next to the balance. | Account flagged as balance_unreconciled; Q9 reports the average together with the number of affected accounts and the total residual, so the reader can size the uncertainty instead of guessing at it.</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>Q7, Q8</t>
+          <t>Q9</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>owner was 11.9 years old when account 9 was opened</t>
+          <t>sum(signed_amount) = 59941.10 but last reported balance = 59939.30 (difference 1.80)</t>
         </is>
       </c>
     </row>
@@ -938,7 +943,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>partner_bank and partner_account are both NULL; operation = VKLAD</t>
+          <t>partner_bank and partner_account are both NULL; operation = NULL</t>
         </is>
       </c>
     </row>
@@ -1088,7 +1093,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>balance_after = -1142.60</t>
+          <t>balance_after = -13466.40</t>
         </is>
       </c>
     </row>
@@ -1627,7 +1632,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>'The balance at the end of December 1998' (Q9) is a modelling decision, not a column: it needs a tie-break for intra-day order and a carry-forward for months with no posting. Both are decided here, once, and marked with is_carried_forward.</t>
+          <t>'The balance at the end of December 1998' (Q9) is a modelling decision, not a column: it needs the closing posting of a day with several (the end of the running-balance chain, D028) and a carry-forward for months with no posting. Both are decided here, once, and marked with closing_basis and is_carried_forward.</t>
         </is>
       </c>
     </row>
@@ -2338,7 +2343,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Builds schema core as a star schema with a bridge: dim_date, dim_district, dim_client, dim_account, bridge_disposition (owner or disponent), dim_card, fact_loan (is_problematic = status B or D), fact_transaction (1,056,319 rows = stg minus 1 quarantined), fact_account_month_end_balance (month-end balance with carry-forward) and ref_codes. Adds curated views v_account_owner, v_loan_enriched, v_client_region. Adds opaque client_ref and account_ref. Then re-applies the ai views (step 7).</t>
+          <t>Builds schema core as a star schema with a bridge: dim_date, dim_district, dim_client, dim_account, bridge_disposition (owner or disponent), dim_card, fact_loan (is_problematic = status B or D), fact_transaction (1,056,319 rows = stg minus 1 quarantined), fact_account_month_end_balance (month-end balance: the closing posting is the end of the day's running-balance chain, D028, with carry-forward) and ref_codes. Adds curated views v_account_owner, v_loan_enriched, v_client_region. Adds opaque client_ref and account_ref. Then re-applies the ai views (step 7).</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -2416,7 +2421,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>The YAML describes each ai entity (grain, key, columns, join paths), the certified metrics, a glossary that says what each term is NOT, and the data-quality caveats with row counts. The build validates it against information_schema: a described column that does not exist, an existing column nobody described, or a grain that is not really one row per key fails the build. It is then rendered into semantic/context_pack.md (about 29,500 characters, 6,900 tokens), which is all the LLM ever sees.</t>
+          <t>The YAML describes each ai entity (grain, key, columns, join paths), the certified metrics, a glossary that says what each term is NOT, and the data-quality caveats with row counts. The build validates it against information_schema: a described column that does not exist, an existing column nobody described, or a grain that is not really one row per key fails the build. It is then rendered into semantic/context_pack.md (about 36,900 characters), which is all the LLM ever sees.</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -2566,22 +2571,22 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>src/run_questions.py, src/llm_client.py, src/sql_guard.py, src/evaluate.py</t>
+          <t>src/run_questions.py, src/llm_client.py, src/sql_guard.py, src/sql_ir.py, src/evaluate.py</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>For each question: (1) the context pack plus the question is sent to the LLM, which has no tools, no database and no files and must answer with one JSON object: sql, reasoning, assumptions, caveats. (2) sqlglot parses the SQL: exactly one read-only statement, only the ai schema, a row cap added, a statement timeout set. (3) It runs as the chosen database user after both factors, so row level security filters the rows. (4) If the output cannot be parsed or the guard rejects it, one retry is allowed with the reason (maximum 2 attempts). (5) Every call is logged in llm_logs/. (6) 'evaluate' compares each answer value-by-value with the reference (tolerance 0.011).</t>
+          <t>For each question: (1) the context pack plus the question is sent to the LLM, which has no tools, no database and no files and must answer with one JSON object: sql, ir (the certified metric, entity, counting grain, half-open periods, grouping, filters it intends), reasoning, assumptions, caveats. (2) sqlglot parses the SQL: exactly one read-only statement, only the ai schema, a row cap added, a statement timeout set. (3) src/sql_ir.py checks the IR against the semantic layer and the SQL against the IR: every column exists, the period filter selects exactly the IR's days, joins are declared and cannot repeat the counted entity, grouping and filters are the ones declared (D029). (4) Only then does it log in as the chosen database user (both factors), have PostgreSQL plan the query, run it under row level security, and recompute the metric from the IR; the two must agree before any row is shown. (5) Any refusal allows one retry with the reason (maximum 2 attempts). (6) Every call is logged in llm_logs/. (7) 'evaluate' compares each verified answer value-by-value with the reference (tolerance 0.011). 'make extra' does the same for the additional gender and quarter questions.</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>dq/results/llm_results.json, dq/results/evaluation.json, llm_logs/Q*_attempt*.json.</t>
+          <t>dq/results/llm_results.json, dq/results/evaluation.json, llm_logs/Q*_attempt*.json; dq/results/*_extra.json and llm_logs/extra/ for the additional questions.</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>The LLM is treated as an untrusted query author: the guard checks the shape, the policy decides the rows.</t>
+          <t>The LLM is treated as an untrusted query author: the guard checks the shape, the IR verifier checks the meaning, the policy decides the rows. A guard pass alone proves nothing about correctness.</t>
         </is>
       </c>
     </row>
@@ -2626,7 +2631,7 @@
       <c r="F18" s="2" t="n"/>
       <c r="G18" s="2" t="n"/>
     </row>
-    <row r="19" ht="45" customHeight="1">
+    <row r="19" ht="60" customHeight="1">
       <c r="A19" s="2" t="n"/>
       <c r="B19" s="10" t="inlineStr">
         <is>
@@ -2635,7 +2640,7 @@
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>The ten recorded answers on tab 4 were generated by Claude Sonnet 5.5 through the Claude CLI, not by Ollama. The code path for Ollama exists and is covered by the provider switch, but the note in src/llm_client.py and in DECISIONS.md D005 says it has never executed in the build environment, because the model download hosts were not reachable there. No Ollama result is claimed anywhere in this workbook.</t>
+          <t>The ten recorded answers on tab 4, and the four additional ones below them, were generated by Claude Sonnet 5.5 through the Claude CLI, not by Ollama. The code path for Ollama exists and is covered by the provider switch, but the note in src/llm_client.py and in DECISIONS.md D005 says it has never executed in the build environment, because the model download hosts were not reachable there; no Ollama server was reachable for the 2026-10-28 re-evaluation either. No Ollama result is claimed anywhere in this workbook.</t>
         </is>
       </c>
       <c r="D19" s="11" t="n"/>
@@ -2663,7 +2668,7 @@
       <c r="F20" s="2" t="n"/>
       <c r="G20" s="2" t="n"/>
     </row>
-    <row r="21" ht="105" customHeight="1">
+    <row r="21" ht="165" customHeight="1">
       <c r="A21" s="2" t="n"/>
       <c r="B21" s="8" t="inlineStr">
         <is>
@@ -2674,9 +2679,10 @@
         <is>
           <t>$env:LLM_PROVIDER = "ollama"
 $env:LLM_MODEL = "qwen2.5-coder:7b"
-scripts\windows.ps1 questions
-scripts\windows.ps1 evaluate
-Optional: $env:OLLAMA_HOST (default http://localhost:11434), $env:LLM_TIMEOUT_SECONDS (default 300). Linux/macOS/WSL: export LLM_PROVIDER=ollama LLM_MODEL=qwen2.5-coder:7b, then make questions.</t>
+.venv\Scripts\python.exe -m src.run_questions --out dq\results\llm_results_ollama.json
+.venv\Scripts\python.exe -m src.evaluate --llm dq\results\llm_results_ollama.json --out dq\results\evaluation_ollama.json
+Additional questions: add --suite extra and use llm_results_extra_ollama.json / evaluation_extra_ollama.json.
+Use separate files like this: the default ones hold the Claude run, and the runner only merges results from the same provider and model. Call logs go to llm_logs\llm_results_ollama\. Optional: $env:OLLAMA_HOST (default http://localhost:11434), $env:LLM_TIMEOUT_SECONDS (default 300). Linux/macOS/WSL: export LLM_PROVIDER=ollama LLM_MODEL=qwen2.5-coder:7b and the same python -m commands.</t>
         </is>
       </c>
       <c r="D21" s="2" t="n"/>
@@ -2710,7 +2716,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>POST /api/generate with the system prompt, the rendered context pack plus the question, stream = false and temperature 0.0 (src/config.py LLM_TEMPERATURE). The reply is parsed as one JSON object {sql, reasoning, assumptions, caveats}.</t>
+          <t>POST /api/generate with the system prompt, the rendered context pack plus the question, stream = false and temperature 0.0 (src/config.py LLM_TEMPERATURE). The reply is parsed as one JSON object {sql, ir, reasoning, assumptions, caveats}.</t>
         </is>
       </c>
       <c r="D23" s="2" t="n"/>
@@ -2718,7 +2724,7 @@
       <c r="F23" s="2" t="n"/>
       <c r="G23" s="2" t="n"/>
     </row>
-    <row r="24" ht="32" customHeight="1">
+    <row r="24" ht="45" customHeight="1">
       <c r="A24" s="2" t="n"/>
       <c r="B24" s="8" t="inlineStr">
         <is>
@@ -2727,7 +2733,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>The semantic layer, the SQL guard, the row cap and timeout, the retry rule (max 2 attempts), the login (password + one-time code) and row level security are identical. A weaker model can therefore write a worse query, but it cannot see rows its logged-in user is not entitled to.</t>
+          <t>The semantic layer, the SQL guard, the IR verifier, the row cap and timeout, the retry rule (max 2 attempts), the login (password + one-time code) and row level security are identical. A weaker model can therefore write a worse query, but the verifier refuses it rather than showing a number it cannot vouch for, and it cannot see rows its logged-in user is not entitled to.</t>
         </is>
       </c>
       <c r="D24" s="2" t="n"/>
@@ -2792,7 +2798,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:K24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2804,6 +2810,8 @@
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="44" customWidth="1" min="10" max="10"/>
+    <col width="40" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2816,7 +2824,7 @@
     <row r="2" ht="48" customHeight="1">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>SQL generated by claude-sonnet-5-5 through the claude_cli provider, executed as database user cro_global (a portfolio holding all clients, still filtered by row level security), at git commit a7da25a. The SQL is unedited. It was NOT generated by Ollama; tab 3 explains how to regenerate it with Ollama. The reference answer is hand-written SQL (sql/60_reference_queries.sql), never shown to the model. Verdict = value-by-value comparison, tolerance 0.011.</t>
+          <t>SQL generated by claude-sonnet-5-5 through the claude_cli provider, executed as database user cro_global (a portfolio holding all clients, still filtered by row level security), at git commit 49059c0. The SQL is unedited. It was NOT generated by Ollama; tab 3 explains how to regenerate it with Ollama. The reference answer is hand-written SQL (sql/60_reference_queries.sql), never shown to the model. Every answer was verified against the intent (IR) the model declared before and after execution (src/sql_ir.py, D029); a guard pass alone is not evidence of a correct answer. Verdict = value-by-value comparison, tolerance 0.011.</t>
         </is>
       </c>
     </row>
@@ -2866,8 +2874,18 @@
           <t>Caveats cited</t>
         </is>
       </c>
-    </row>
-    <row r="5" ht="169" customHeight="1">
+      <c r="J4" s="1" t="inlineStr">
+        <is>
+          <t>Declared intent (IR)</t>
+        </is>
+      </c>
+      <c r="K4" s="1" t="inlineStr">
+        <is>
+          <t>Intent check</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="143" customHeight="1">
       <c r="A5" s="8" t="inlineStr">
         <is>
           <t>Q1</t>
@@ -2887,21 +2905,20 @@
 GROUP BY
   region
 ORDER BY
-  client_count DESC,
   region
 LIMIT 10000</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>region=south Moravia | client_count=937
-region=north Moravia | client_count=920
+          <t>region=Prague | client_count=663
 region=central Bohemia | client_count=664
-region=Prague | client_count=663
 region=east Bohemia | client_count=660
 region=north Bohemia | client_count=561
-region=west Bohemia | client_count=515
-region=south Bohemia | client_count=449</t>
+region=north Moravia | client_count=920
+region=south Bohemia | client_count=449
+region=south Moravia | client_count=937
+region=west Bohemia | client_count=515</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -2926,10 +2943,10 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>I used ai.client with its own region column, because the question is about clients and the client's region means the district where the client lives (assumption A1). I did not use ai.account.region, and I did not join through accounts. ai.client has one row per client, so count(*) is the certified client_count and needs no DISTINCT. The count includes clients who hold no account or are only disponents.
-- 'Clients' means every client row in ai.client, including clients with no account and clients who are only disponents.
-- 'Region' means the region the client lives in (ai.client.region), not the region of an account they own.
-- Counts cover only the clients the caller is entitled to see. If the caller is a self-service customer, the result shows one client, not a bank-wide total.</t>
+          <t>The question is about clients, so I used ai.client with the certified client_count metric (count(*)) and grouped by the client's own region (ai.client.region), not the account's region. I did not join to ai.account_owner, which would drop the 869 clients who own no account and would repeat clients that own several accounts.
+- 'Clients' means every client visible to the caller, including clients who hold no account or are only disponents.
+- Region means the region where the client lives (ai.client.region).
+- The count covers only the clients the caller is entitled to see. A self-service customer would therefore see only their own single client row, not a bank-wide total.</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -2937,8 +2954,29 @@
           <t>C4</t>
         </is>
       </c>
-    </row>
-    <row r="6" ht="208" customHeight="1">
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>{
+ "metric": "client_count",
+ "entity": "ai.client",
+ "counting_grain": "client_id",
+ "time": null,
+ "group_by": [
+  "region"
+ ],
+ "filters": [],
+ "order": null,
+ "limit": null
+}</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>VERIFIED: ir, columns, entity, joins, measure, grouping, filters, limit, guard, plan, recompute</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="169" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
           <t>Q2</t>
@@ -2952,10 +2990,13 @@
       <c r="C6" s="9" t="inlineStr">
         <is>
           <t>SELECT
-  l.loan_year,
-  COUNT(*) AS loan_count,
-  SUM(l.amount) AS total_loan_amount
+  l.loan_year AS loan_year,
+  SUM(l.amount) AS total_loan_amount,
+  COUNT(*) AS loan_count
 FROM ai.loan AS l
+WHERE
+  l.loan_date &gt;= CAST('1993-01-01' AS DATE)
+  AND l.loan_date &lt; CAST('1999-01-01' AS DATE)
 GROUP BY
   l.loan_year
 ORDER BY
@@ -2965,12 +3006,12 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>loan_year=1993 | loan_count=20 | total_loan_amount=2619276.0
-loan_year=1994 | loan_count=101 | total_loan_amount=13379904.0
-loan_year=1995 | loan_count=90 | total_loan_amount=13344372.0
-loan_year=1996 | loan_count=117 | total_loan_amount=18317676.0
-loan_year=1997 | loan_count=196 | total_loan_amount=30731364.0
-loan_year=1998 | loan_count=158 | total_loan_amount=24869148.0</t>
+          <t>loan_year=1993 | total_loan_amount=2619276.0 | loan_count=20
+loan_year=1994 | total_loan_amount=13379904.0 | loan_count=101
+loan_year=1995 | total_loan_amount=13344372.0 | loan_count=90
+loan_year=1996 | total_loan_amount=18317676.0 | loan_count=117
+loan_year=1997 | total_loan_amount=30731364.0 | loan_count=196
+loan_year=1998 | total_loan_amount=24869148.0 | loan_count=158</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -2993,11 +3034,11 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>I used ai.loan because it has one row per loan, and loan_year is already materialised, so no join is needed. I summed amount, which is the principal and matches the certified total_loan_amount metric. I did not use monthly_payment * duration_months, which includes interest. I grouped by loan_year, which is the year of loan_date (the date a loan is granted), and I returned loan_count beside each sum so the volume behind it is visible.
-- 'Granted' means the loan start date (loan_date), so each loan is counted in the year of loan_date.
+          <t>ai.loan is the pre-joined loan entity and total_loan_amount (sum of principal amount) is certified on it, grouped by the materialised loan_year and filtered on loan_date over the full book window. No join to ai.transaction is used, so there is no fan-out, and the principal is summed rather than monthly_payment * duration_months.
+- 'Per year' means calendar year of loan_date (the date the loan was granted), across the whole book 1993-1998.
+- Years in which no loans were granted would not appear, since ai.calendar is not joined (the certified permitted join is optional here and would require grouping by the calendar year); loan_count is shown as supporting context.
 - Amounts are in CZK and are not rounded.
-- Only years that have at least one loan appear in the result. The question does not ask for a per-calendar-period series, so I did not join ai.calendar, and a year with no loans would be omitted rather than shown as zero.
-- Results cover only the clients the caller is entitled to see, so the totals describe their portfolio. They may not be bank-wide totals.</t>
+- Results cover only the clients the caller is entitled to see.</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -3005,8 +3046,37 @@
           <t>-</t>
         </is>
       </c>
-    </row>
-    <row r="7" ht="117" customHeight="1">
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>{
+ "metric": "total_loan_amount",
+ "entity": "ai.loan",
+ "counting_grain": "loan_id",
+ "time": {
+  "column": "loan_date",
+  "periods": [
+   {
+    "from": "1993-01-01",
+    "to": "1999-01-01"
+   }
+  ]
+ },
+ "group_by": [
+  "loan_year"
+ ],
+ "filters": [],
+ "order": "asc",
+ "limit": null
+}</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>VERIFIED: ir, columns, entity, joins, periods, measure, grouping, filters, limit, guard, plan, recompute</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="130" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
         <is>
           <t>Q3</t>
@@ -3024,14 +3094,14 @@
   COUNT(*) FILTER(WHERE
     is_problematic) AS problematic_loan_count,
   ROUND(CAST(100.0 * COUNT(*) FILTER(WHERE
-    is_problematic) / COUNT(*) AS DECIMAL), 2) AS problematic_loan_share_pct
+    is_problematic) / COUNT(*) AS DECIMAL), 2) AS problematic_loan_share
 FROM ai.loan
 LIMIT 10000</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>loan_count=682 | problematic_loan_count=76 | problematic_loan_share_pct=11.14</t>
+          <t>loan_count=682 | problematic_loan_count=76 | problematic_loan_share=11.14</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -3049,9 +3119,10 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>I used ai.loan, which has one row per loan and the certified boolean is_problematic (status B or D). I applied the certified problematic_loan_share expression as written and returned the total loan count and the problematic count beside it, so the denominator is visible. I did not redefine problematic from status_code.
-- 'Our loans' means all loans the caller is entitled to see, so the percentage describes the caller's own portfolio rather than the whole bank.
-- No time period was given, so all loans in the 1993-1998 book are included.</t>
+          <t>ai.loan carries the certified is_problematic flag (status B or D), so I used the certified problematic_loan_share expression verbatim with no joins. I returned the total loan count and the problematic loan count beside the percentage so the denominator is visible, and did not redefine problematic from status_code.
+- No time period was specified, so all loans in the book (1993-1998) are included.
+- The share is computed over the loans the caller is entitled to see, so it describes their portfolio, not necessarily the whole bank.
+- 'Problematic' means status B (finished, unpaid) or D (running, client in debt).</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -3059,8 +3130,27 @@
           <t>-</t>
         </is>
       </c>
-    </row>
-    <row r="8" ht="169" customHeight="1">
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>{
+ "metric": "problematic_loan_share",
+ "entity": "ai.loan",
+ "counting_grain": "loan_id",
+ "time": null,
+ "group_by": [],
+ "filters": [],
+ "order": null,
+ "limit": null
+}</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>VERIFIED: ir, columns, entity, joins, measure, grouping, filters, limit, guard, plan, recompute</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="143" customHeight="1">
       <c r="A8" s="8" t="inlineStr">
         <is>
           <t>Q4</t>
@@ -3075,8 +3165,8 @@
         <is>
           <t>SELECT
   owner_card_type,
-  COUNT(*) AS loan_count,
-  ROUND(CAST(AVG(amount) AS DECIMAL), 2) AS average_loan_amount
+  ROUND(CAST(AVG(amount) AS DECIMAL), 2) AS average_loan_amount,
+  COUNT(*) AS loan_count
 FROM ai.loan
 GROUP BY
   owner_card_type
@@ -3087,10 +3177,10 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>owner_card_type=classic | loan_count=133 | average_loan_amount=148808.57
-owner_card_type=gold | loan_count=16 | average_loan_amount=161880.75
-owner_card_type=junior | loan_count=21 | average_loan_amount=221970.29
-owner_card_type=no card | loan_count=512 | average_loan_amount=148864.71</t>
+          <t>owner_card_type=classic | average_loan_amount=148808.57 | loan_count=133
+owner_card_type=gold | average_loan_amount=161880.75 | loan_count=16
+owner_card_type=junior | average_loan_amount=221970.29 | loan_count=21
+owner_card_type=no card | average_loan_amount=148864.71 | loan_count=512</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -3111,10 +3201,10 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>I used ai.loan because it already carries the account owner's card type, with the literal 'no card' where the owner has none. Every loan therefore falls into exactly one group, and I did not join ai.card, which would include disponents' cards. The average is the certified average_loan_amount, round(avg(amount), 2), on the principal, and the loan count sits next to it so the denominator is visible.
-- 'Card type of the account owner' means ai.loan.owner_card_type, so owners with no card appear as the group 'no card'.
-- 'Loan amount' means the principal (amount) in CZK, not monthly_payment * duration_months.
-- Results cover only the loans the caller is entitled to see. A self-service customer would see only their own loans, so the groups would not be bank-wide.</t>
+          <t>ai.loan is pre-joined to the account owner's card type, with 'no card' already covering owners without a card, so grouping by owner_card_type places every loan in exactly one group without joining ai.card (which could include disponents' cards). I used the certified average_loan_amount expression verbatim at loan grain, with the loan count beside it to show the denominator.
+- No time restriction was requested, so all loans in the book (1993-1998) are included.
+- Card type means the account OWNER's card; owners without a card appear as 'no card'.
+- Amounts are in CZK and the results cover only the clients the caller is entitled to see.</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -3122,8 +3212,29 @@
           <t>-</t>
         </is>
       </c>
-    </row>
-    <row r="9" ht="260" customHeight="1">
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>{
+ "metric": "average_loan_amount",
+ "entity": "ai.loan",
+ "counting_grain": "loan_id",
+ "time": null,
+ "group_by": [
+  "owner_card_type"
+ ],
+ "filters": [],
+ "order": null,
+ "limit": null
+}</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>VERIFIED: ir, columns, entity, joins, measure, grouping, filters, limit, guard, plan, recompute</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="182" customHeight="1">
       <c r="A9" s="8" t="inlineStr">
         <is>
           <t>Q5</t>
@@ -3137,39 +3248,33 @@
       <c r="C9" s="9" t="inlineStr">
         <is>
           <t>SELECT
-  t.account_district_id,
-  t.account_district_name,
-  t.account_region,
-  SUM(t.amount) AS incoming_amount_czk,
-  COUNT(*) AS credit_postings,
-  COUNT(DISTINCT t.account_id) AS accounts_with_credits
-FROM ai.transaction AS t
+  account_district_name AS district_name,
+  SUM(amount) AS incoming_transaction_amount,
+  COUNT(*) AS credit_postings
+FROM ai.transaction
 WHERE
-  t.direction = 'credit'
-  AND t.trans_date &gt;= CAST('1997-01-01' AS DATE)
-  AND t.trans_date &lt; CAST('1998-01-01' AS DATE)
+  direction = 'credit'
+  AND trans_date &gt;= CAST('1997-01-01' AS DATE)
+  AND trans_date &lt; CAST('1998-01-01' AS DATE)
 GROUP BY
-  t.account_district_id,
-  t.account_district_name,
-  t.account_region
+  account_district_name
 ORDER BY
-  SUM(t.amount) DESC,
-  t.account_district_name ASC
+  incoming_transaction_amount DESC
 LIMIT 10</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>account_district_id=1 | account_district_name=Hl.m. Praha | account_region=Prague | incoming_amount_czk=115130200.1 | credit_postings=13611 | accounts_with_credits=554
-account_district_id=70 | account_district_name=Karvina | account_region=north Moravia | incoming_amount_czk=28506437.1 | credit_postings=3802 | accounts_with_credits=152
-account_district_id=74 | account_district_name=Ostrava - mesto | account_region=north Moravia | incoming_amount_czk=27689271.9 | credit_postings=3378 | accounts_with_credits=135
-account_district_id=54 | account_district_name=Brno - mesto | account_region=south Moravia | incoming_amount_czk=23095083.4 | credit_postings=3041 | accounts_with_credits=128
-account_district_id=64 | account_district_name=Zlin | account_region=south Moravia | incoming_amount_czk=19723168.5 | credit_postings=2299 | accounts_with_credits=92
-account_district_id=68 | account_district_name=Frydek - Mistek | account_region=north Moravia | incoming_amount_czk=19087598.8 | credit_postings=2006 | accounts_with_credits=83
-account_district_id=72 | account_district_name=Olomouc | account_region=north Moravia | incoming_amount_czk=15916397.0 | credit_postings=2129 | accounts_with_credits=88
-account_district_id=5 | account_district_name=Kolin | account_region=central Bohemia | incoming_amount_czk=14471603.6 | credit_postings=1542 | accounts_with_credits=65
-account_district_id=52 | account_district_name=Usti nad Orlici | account_region=east Bohemia | incoming_amount_czk=14085167.4 | credit_postings=1431 | accounts_with_credits=57
-account_district_id=19 | account_district_name=Prachatice | account_region=south Bohemia | incoming_amount_czk=12163147.0 | credit_postings=1359 | accounts_with_credits=55</t>
+          <t>district_name=Hl.m. Praha | incoming_transaction_amount=115130200.1 | credit_postings=13611
+district_name=Karvina | incoming_transaction_amount=28506437.1 | credit_postings=3802
+district_name=Ostrava - mesto | incoming_transaction_amount=27689271.9 | credit_postings=3378
+district_name=Brno - mesto | incoming_transaction_amount=23095083.4 | credit_postings=3041
+district_name=Zlin | incoming_transaction_amount=19723168.5 | credit_postings=2299
+district_name=Frydek - Mistek | incoming_transaction_amount=19087598.8 | credit_postings=2006
+district_name=Olomouc | incoming_transaction_amount=15916397.0 | credit_postings=2129
+district_name=Kolin | incoming_transaction_amount=14471603.6 | credit_postings=1542
+district_name=Usti nad Orlici | incoming_transaction_amount=14085167.4 | credit_postings=1431
+district_name=Prachatice | incoming_transaction_amount=12163147.0 | credit_postings=1359</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -3196,20 +3301,55 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>I used ai.transaction, which already carries the account's district and region, and applied the certified incoming_transaction_amount definition: sum(amount) where direction = 'credit'. I summed the positive amount rather than signed_amount, and grouped by the account's district rather than the owner's district, because this is money arriving at accounts. 1997 is a half-open date range, and the ranking has a deterministic tie-break.
-- 'Districts' means the district the account is registered in (account_district_name), not where the account owner lives.
-- '1997' is calendar year 1997 by trans_date, from 1997-01-01 to 1997-12-31 inclusive.
-- Amounts are in CZK, and the ranking covers only the clients the caller is entitled to see. A client-type caller sees only their own data, so this would not be a bank-wide ranking.
-- I included the posting count and distinct account count next to each total so the size of each district's base is visible.</t>
+          <t>ai.transaction carries the account's district name and direction, so the certified incoming_transaction_amount metric (sum of positive amount where direction = 'credit') is grouped by the account's district with no joins, which avoids any fan-out. Time is filtered on trans_date with a half-open range for calendar year 1997, and amount (not signed_amount) is summed.
+- 'District' means the district the account is registered in (account_district_name), as the money arrives at accounts, not where the client lives.
+- Ranking is by total incoming amount descending; ties at rank 10 are cut arbitrarily by LIMIT.
+- Results cover only the clients the caller is entitled to see, so the ranking reflects their portfolio.
+- Amounts are in CZK and are not rounded.</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>C5, C7</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="299" customHeight="1">
+          <t>C5, C6, C7</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>{
+ "metric": "incoming_transaction_amount",
+ "entity": "ai.transaction",
+ "counting_grain": "trans_id",
+ "time": {
+  "column": "trans_date",
+  "periods": [
+   {
+    "from": "1997-01-01",
+    "to": "1998-01-01"
+   }
+  ]
+ },
+ "group_by": [
+  "account_district_name"
+ ],
+ "filters": [
+  {
+   "column": "direction",
+   "op": "=",
+   "value": "credit"
+  }
+ ],
+ "order": "desc",
+ "limit": 10
+}</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>VERIFIED: ir, columns, entity, joins, periods, measure, grouping, filters, limit, guard, plan, recompute</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="182" customHeight="1">
       <c r="A10" s="8" t="inlineStr">
         <is>
           <t>Q6</t>
@@ -3224,43 +3364,34 @@
         <is>
           <t>SELECT
   c.year_month AS month,
-  c.month_start,
-  COUNT(a.account_id) AS new_accounts
-FROM (
-  SELECT DISTINCT
-    year_month,
-    month_start
-  FROM ai.calendar
-  WHERE
-    year = 1996
-) AS c
+  COUNT(a.account_id) AS account_count
+FROM ai.calendar AS c
 LEFT JOIN ai.account AS a
-  ON a.open_date &gt;= c.month_start
-  AND a.open_date &lt; (
-    c.month_start + INTERVAL '1 MONTH'
-  )
+  ON a.open_date = c.date_key
+WHERE
+  c.date_key &gt;= CAST('1996-01-01' AS DATE)
+  AND c.date_key &lt; CAST('1997-01-01' AS DATE)
 GROUP BY
-  c.year_month,
-  c.month_start
+  c.year_month
 ORDER BY
-  c.month_start
+  c.year_month
 LIMIT 10000</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>month=1996-01 | month_start=1996-01-01 | new_accounts=106
-month=1996-02 | month_start=1996-02-01 | new_accounts=104
-month=1996-03 | month_start=1996-03-01 | new_accounts=124
-month=1996-04 | month_start=1996-04-01 | new_accounts=101
-month=1996-05 | month_start=1996-05-01 | new_accounts=91
-month=1996-06 | month_start=1996-06-01 | new_accounts=113
-month=1996-07 | month_start=1996-07-01 | new_accounts=137
-month=1996-08 | month_start=1996-08-01 | new_accounts=133
-month=1996-09 | month_start=1996-09-01 | new_accounts=108
-month=1996-10 | month_start=1996-10-01 | new_accounts=115
-month=1996-11 | month_start=1996-11-01 | new_accounts=106
-month=1996-12 | month_start=1996-12-01 | new_accounts=125</t>
+          <t>month=1996-01 | account_count=106
+month=1996-02 | account_count=104
+month=1996-03 | account_count=124
+month=1996-04 | account_count=101
+month=1996-05 | account_count=91
+month=1996-06 | account_count=113
+month=1996-07 | account_count=137
+month=1996-08 | account_count=133
+month=1996-09 | account_count=108
+month=1996-10 | account_count=115
+month=1996-11 | account_count=106
+month=1996-12 | account_count=125</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -3289,18 +3420,47 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>I used ai.account, where open_date defines a new account, and joined it to ai.calendar so that months with no new accounts come back as 0 instead of being left out (QR6). I built the 12 months of 1996 from the calendar and LEFT JOINed accounts by open_date range. COUNT(a.account_id) counts only matched accounts, so empty months show 0.
-- 'Per month in 1996' means calendar months January to December 1996, based on account open_date.
-- Counts cover only the accounts the caller is entitled to see, so a self-service customer would see only their own accounts.</t>
+          <t>Used ai.account (new account = open_date in the period) with the certified account_count metric, counting account_id. Joined ai.calendar from the calendar side with a LEFT JOIN so months with no new accounts return 0 rather than being omitted, and used count(a.account_id) so empty months are not counted as 1.
+- 'New accounts' means accounts whose open_date falls in 1996, grouped by calendar month.
+- Counts cover only the clients/accounts the caller is entitled to see, so they are a portfolio figure rather than a bank-wide total.</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="325" customHeight="1">
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>{
+ "metric": "account_count",
+ "entity": "ai.account",
+ "counting_grain": "account_id",
+ "time": {
+  "column": "open_date",
+  "periods": [
+   {
+    "from": "1996-01-01",
+    "to": "1997-01-01"
+   }
+  ]
+ },
+ "group_by": [
+  "month"
+ ],
+ "filters": [],
+ "order": "asc",
+ "limit": null
+}</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>VERIFIED: ir, columns, entity, joins, periods, measure, grouping, filters, limit, guard, plan, recompute</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="299" customHeight="1">
       <c r="A11" s="8" t="inlineStr">
         <is>
           <t>Q7</t>
@@ -3315,13 +3475,8 @@
         <is>
           <t>SELECT
   loan_status,
-  status_code,
+  ROUND(CAST(AVG(owner_age_at_loan_start) AS DECIMAL), 2) AS average_age_at_loan_start,
   COUNT(*) AS loan_count,
-  ROUND(CAST(AVG(owner_age_at_loan_start) AS DECIMAL), 2) AS average_age_at_loan_start,
-  COUNT(*) FILTER(WHERE
-    'val_owner_age_at_loan_start' = ANY(
-      data_quality_flags
-    )) AS flagged_under_15_loans,
   ROUND(
     CAST(AVG(owner_age_at_loan_start) FILTER(WHERE
       NOT (
@@ -3330,22 +3485,25 @@
         )
       )) AS DECIMAL),
     2
-  ) AS average_age_excluding_flagged
+  ) AS average_age_excluding_flagged,
+  COUNT(*) FILTER(WHERE
+    'val_owner_age_at_loan_start' = ANY(
+      data_quality_flags
+    )) AS flagged_under_15_loans
 FROM ai.loan
 GROUP BY
-  loan_status,
-  status_code
+  loan_status
 ORDER BY
-  status_code
+  loan_status
 LIMIT 10000</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>loan_status=finished, paid in full | status_code=A | loan_count=203 | average_age_at_loan_start=37.07 | flagged_under_15_loans=4 | average_age_excluding_flagged=37.53
-loan_status=finished, unpaid (default) | status_code=B | loan_count=31 | average_age_at_loan_start=39.61 | flagged_under_15_loans=0 | average_age_excluding_flagged=39.61
-loan_status=running, no problem | status_code=C | loan_count=403 | average_age_at_loan_start=38.7 | flagged_under_15_loans=2 | average_age_excluding_flagged=38.82
-loan_status=running, client in debt | status_code=D | loan_count=45 | average_age_at_loan_start=37.0 | flagged_under_15_loans=0 | average_age_excluding_flagged=37.0</t>
+          <t>loan_status=finished, paid in full | average_age_at_loan_start=37.07 | loan_count=203 | average_age_excluding_flagged=37.53 | flagged_under_15_loans=4
+loan_status=finished, unpaid (default) | average_age_at_loan_start=39.61 | loan_count=31 | average_age_excluding_flagged=39.61 | flagged_under_15_loans=0
+loan_status=running, client in debt | average_age_at_loan_start=37.0 | loan_count=45 | average_age_excluding_flagged=37.0 | flagged_under_15_loans=0
+loan_status=running, no problem | average_age_at_loan_start=38.7 | loan_count=403 | average_age_excluding_flagged=38.82 | flagged_under_15_loans=2</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -3366,11 +3524,10 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>I used ai.loan because it already carries the pre-computed exact owner_age_at_loan_start and the business-language loan_status, so no joins or birth-date arithmetic are needed. I used the certified average_age_at_loan_start expression verbatim, grouped by loan status. I also return the loan count per status and the average with and without the 6 flagged under-15 loans, as caveat C3 requires.
-- 'Loan status' means the four statuses in ai.loan.loan_status (grouped with status_code for ordering), not the problematic/non-problematic split.
-- Results cover only the loans the caller is entitled to see, so the averages describe their portfolio.
-- Ages are in years, including the fractional part, rounded to two decimals.
-- A flagged loan is one whose data_quality_flags contains 'val_owner_age_at_loan_start'. data_quality_flags is assumed to be a non-null array, which the layer describes as an empty array when clean.</t>
+          <t>ai.loan carries the pre-computed owner_age_at_loan_start and the business-language loan_status, so no joins are needed. I used the certified average expression verbatim without recomputing age from birth dates, grouped to one row per status, and added loan counts plus an average excluding the flagged under-15 owners per caveat C3.
+- 'Per loan status' means grouping by the business-language loan_status (equivalent to the four status codes A-D).
+- No time period was requested, so all loans in the book (1993-1998) visible to the caller are included.
+- The extra columns (loan counts, average excluding flagged loans) are supporting figures; the certified average is the first metric column.</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -3378,8 +3535,29 @@
           <t>C3</t>
         </is>
       </c>
-    </row>
-    <row r="12" ht="169" customHeight="1">
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>{
+ "metric": "average_age_at_loan_start",
+ "entity": "ai.loan",
+ "counting_grain": "loan_id",
+ "time": null,
+ "group_by": [
+  "loan_status"
+ ],
+ "filters": [],
+ "order": null,
+ "limit": null
+}</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>VERIFIED: ir, columns, entity, joins, measure, grouping, filters, limit, guard, plan, recompute</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="156" customHeight="1">
       <c r="A12" s="8" t="inlineStr">
         <is>
           <t>Q8</t>
@@ -3393,10 +3571,9 @@
       <c r="C12" s="9" t="inlineStr">
         <is>
           <t>SELECT
-  owner_gender AS gender,
+  owner_gender,
   COUNT(*) AS owner_count,
-  ROUND(CAST(100.0 * COUNT(*) / SUM(COUNT(*)) OVER () AS DECIMAL), 2) AS share_pct,
-  SUM(COUNT(*)) OVER () AS total_gold_card_owners
+  ROUND(CAST(100.0 * COUNT(*) / SUM(COUNT(*)) OVER () AS DECIMAL), 2) AS gender_share_pct
 FROM ai.account_owner
 WHERE
   owner_card_type = 'gold'
@@ -3409,8 +3586,8 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>gender=female | owner_count=35 | share_pct=39.77 | total_gold_card_owners=88.0
-gender=male | owner_count=53 | share_pct=60.23 | total_gold_card_owners=88.0</t>
+          <t>owner_gender=female | owner_count=35 | gender_share_pct=39.77
+owner_gender=male | owner_count=53 | gender_share_pct=60.23</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -3429,19 +3606,46 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>I used ai.account_owner because it already resolves the owner's own card. A card held by a disponent is deliberately excluded, so there is no need to join ai.card. I applied the certified gender_share expression, and I return the counts and the total next to the percentages so the denominator is visible.
-- 'Gender split' means the share of gold-card-holding account owners by gender, with each account counted once (the entity has one row per account).
-- An owner with gold cards on more than one account would be counted once per account. The entity's grain is the account, and the layer doesn't say whether this happens.
-- Results cover only the clients the caller is entitled to see, so the split describes their portfolio. A self-service customer would see at most themselves.</t>
+          <t>I used ai.account_owner, which already resolves the owner's own card, and grouped by owner_gender with the certified gender_share expression. I filtered on owner_card_type = 'gold' and did not use ai.card, so a gold card held by a disponent doesn't count.
+- 'Account owners holding a gold card' means owners whose own card is gold (owner_card_type = 'gold'), not disponents with a gold card.
+- No time period was asked about, so no date filter is applied.
+- The split covers only the clients the caller is entitled to see, so it describes their portfolio.</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="182" customHeight="1">
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>{
+ "metric": "gender_share",
+ "entity": "ai.account_owner",
+ "counting_grain": "account_id",
+ "time": null,
+ "group_by": [
+  "owner_gender"
+ ],
+ "filters": [
+  {
+   "column": "owner_card_type",
+   "op": "=",
+   "value": "gold"
+  }
+ ],
+ "order": null,
+ "limit": null
+}</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>VERIFIED: ir, columns, entity, joins, measure, grouping, filters, limit, guard, plan, recompute</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="156" customHeight="1">
       <c r="A13" s="8" t="inlineStr">
         <is>
           <t>Q9</t>
@@ -3455,29 +3659,27 @@
       <c r="C13" s="9" t="inlineStr">
         <is>
           <t>SELECT
-  CAST('1998-12-31' AS DATE) AS month_end_date,
   ROUND(CAST(AVG(closing_balance) AS DECIMAL), 2) AS average_month_end_balance,
   COUNT(*) AS accounts_with_balance,
   COUNT(*) FILTER(WHERE
-    is_carried_forward) AS carried_forward_balances,
+    is_carried_forward) AS carried_forward_count,
   COUNT(*) FILTER(WHERE
-    'con_balance_reconciliation_material' = ANY(
-      account_data_quality_flags
-    )) AS accounts_with_reconciliation_flag
+    closing_basis = 'ambiguous') AS ambiguous_count
 FROM ai.account_month_end_balance
 WHERE
-  month_end_date = CAST('1998-12-31' AS DATE)
+  month_end_date &gt;= CAST('1998-12-31' AS DATE)
+  AND month_end_date &lt; CAST('1999-01-01' AS DATE)
 LIMIT 10000</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>month_end_date=1998-12-31 | average_month_end_balance=43808.94 | accounts_with_balance=4500 | carried_forward_balances=76 | accounts_with_reconciliation_flag=55</t>
+          <t>average_month_end_balance=43810.47 | accounts_with_balance=4500 | carried_forward_count=76 | ambiguous_count=42</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>accounts_with_known_balance=4500 | average_balance=43808.94 | median_balance=38494.55 | min_balance=-25821.2 | max_balance=138317.2 | accounts_carried_forward=76 | accounts_balance_unreconciled=55 | accounts_overdrawn=39</t>
+          <t>accounts_with_known_balance=4500 | average_balance=43810.47 | median_balance=38494.55 | min_balance=-25821.2 | max_balance=137829.5 | accounts_carried_forward=76 | accounts_balance_unreconciled=14 | accounts_overdrawn=39 | accounts_closing_ambiguous=42</t>
         </is>
       </c>
       <c r="F13" s="12" t="inlineStr">
@@ -3490,10 +3692,10 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>I used ai.account_month_end_balance, which already applies the tie-break (highest transaction id) and the carry-forward, instead of working out balances from ai.transaction. I applied the certified average_month_end_balance expression, round(avg(closing_balance), 2), filtered to month_end_date = 1998-12-31. I did not count accounts with no balance as zero, and I return the account count and the carried-forward count beside the average.
-- 'End of December 1998' means the month-end date 1998-12-31, the last day of the book.
-- 'Average account balance' means the average closing balance across accounts that have a known balance on that date, in CZK.
-- The result covers only the clients the caller is entitled to see, so it describes their portfolio and not necessarily the whole bank.</t>
+          <t>The ai.account_month_end_balance entity already applies the closing-posting rule and carry-forward, so I used the certified average_month_end_balance metric on it instead of computing balances from ai.transaction. The filter selects only the 1998-12-31 month end with a half-open range. Accounts with no balance are not in the entity, so they are not counted as zero, and the supporting counts are returned beside the average.
+- 'End of December 1998' means the month end 1998-12-31, the last day of the book.
+- The average covers accounts with a known balance on that date, limited to the clients the caller is entitled to see.
+- closing_basis = 'ambiguous' is counted to show how many balances depend on the documented fallback.</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -3501,8 +3703,35 @@
           <t>C1, C2</t>
         </is>
       </c>
-    </row>
-    <row r="14" ht="182" customHeight="1">
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>{
+ "metric": "average_month_end_balance",
+ "entity": "ai.account_month_end_balance",
+ "counting_grain": "account_id, month_end_date",
+ "time": {
+  "column": "month_end_date",
+  "periods": [
+   {
+    "from": "1998-12-31",
+    "to": "1999-01-01"
+   }
+  ]
+ },
+ "group_by": [],
+ "filters": [],
+ "order": null,
+ "limit": null
+}</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>VERIFIED: ir, columns, entity, joins, periods, measure, grouping, filters, limit, guard, plan, recompute</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="169" customHeight="1">
       <c r="A14" s="8" t="inlineStr">
         <is>
           <t>Q10</t>
@@ -3521,21 +3750,20 @@
   COUNT(*) FILTER(WHERE
     is_problematic) AS problematic_loan_count,
   ROUND(CAST(100.0 * COUNT(*) FILTER(WHERE
-    is_problematic) / COUNT(*) AS DECIMAL), 2) AS problematic_loan_share_pct
+    is_problematic) / COUNT(*) AS DECIMAL), 2) AS problematic_loan_share
 FROM ai.loan
 GROUP BY
   statement_frequency
 ORDER BY
-  problematic_loan_share_pct DESC,
-  statement_frequency
+  problematic_loan_share DESC
 LIMIT 10000</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>statement_frequency=after transaction | loan_count=32 | problematic_loan_count=6 | problematic_loan_share_pct=18.75
-statement_frequency=weekly | loan_count=91 | problematic_loan_count=11 | problematic_loan_share_pct=12.09
-statement_frequency=monthly | loan_count=559 | problematic_loan_count=59 | problematic_loan_share_pct=10.55</t>
+          <t>statement_frequency=after transaction | loan_count=32 | problematic_loan_count=6 | problematic_loan_share=18.75
+statement_frequency=weekly | loan_count=91 | problematic_loan_count=11 | problematic_loan_share=12.09
+statement_frequency=monthly | loan_count=559 | problematic_loan_count=59 | problematic_loan_share=10.55</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -3555,15 +3783,36 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>I used ai.loan because it already carries statement_frequency and the certified is_problematic flag, so no joins are needed. I computed the within-group rate (problematic loans divided by all loans of that frequency) with the certified problematic_loan_share expression, not each group's share of all problematic loans. I return the full ranking with loan counts and problematic counts so the size of each denominator is visible, and the top row is the answer.
-- 'Share of problematic loans' means the within-group rate: problematic loans divided by all loans with that statement frequency.
-- The result covers only the loans the caller is entitled to see, so the shares describe their portfolio. A customer-level caller would see at most their own loans.
-- Groups with few loans can produce extreme percentages, so the counts should be read next to each share.</t>
+          <t>Used ai.loan, which already carries statement_frequency, and the certified problematic_loan_share expression with is_problematic, grouped by statement_frequency. The share is a within-group rate (problematic loans over all loans of that frequency), and I return the full ranking with both counts so the denominators are visible, rather than only the top row.
+- No time restriction was asked for, so all loans in the caller's entitled portfolio are included.
+- The result is computed over the loans the caller is entitled to see, so it describes their portfolio.
+- The highest share is the first row of the ranking; small groups may have unstable shares, so read it with the loan_count column.</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
           <t>-</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>{
+ "metric": "problematic_loan_share",
+ "entity": "ai.loan",
+ "counting_grain": "loan_id",
+ "time": null,
+ "group_by": [
+  "statement_frequency"
+ ],
+ "filters": [],
+ "order": "desc",
+ "limit": null
+}</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>VERIFIED: ir, columns, entity, joins, measure, grouping, filters, limit, guard, plan, recompute</t>
         </is>
       </c>
     </row>
@@ -3579,9 +3828,401 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" s="14" t="inlineStr">
+        <is>
+          <t>Additional questions, not in the brief: gender of loans and calendar quarters (sql/61_reference_extra.sql; assumptions A47, A48). Same provider, same checks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="156" customHeight="1">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>E1</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Find male or female loans in Q1 1995.</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>SELECT
+  owner_gender,
+  COUNT(*) AS loan_count
+FROM ai.loan
+WHERE
+  loan_date &gt;= CAST('1995-01-01' AS DATE)
+  AND loan_date &lt; CAST('1995-04-01' AS DATE)
+GROUP BY
+  owner_gender
+ORDER BY
+  owner_gender
+LIMIT 10000</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>owner_gender=female | loan_count=10
+owner_gender=male | loan_count=18</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>gender=female | loans=10 | distinct_loans=10 | total_amount=1199448.0
+gender=male | loans=18 | distinct_loans=18 | total_amount=3034104.0</t>
+        </is>
+      </c>
+      <c r="F19" s="12" t="inlineStr">
+        <is>
+          <t>match</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>The question asks for loans split by male/female in Q1 1995, so I used ai.loan with the certified loan_count metric grouped by owner_gender (the account owner's gender). Q1 is read as calendar January-March, filtered on loan_date with a half-open range, and no join to transactions or cards is used, so there is no fan-out.
+- 'Find male or female loans' is read as the number of loans per gender of the account owner, returned as one row per gender.
+- Q1 1995 means the calendar quarter 1 January to 31 March 1995.
+- Results cover only the clients the caller is entitled to see.</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>{
+ "metric": "loan_count",
+ "entity": "ai.loan",
+ "counting_grain": "loan_id",
+ "time": {
+  "column": "loan_date",
+  "periods": [
+   {
+    "from": "1995-01-01",
+    "to": "1995-04-01"
+   }
+  ]
+ },
+ "group_by": [
+  "owner_gender"
+ ],
+ "filters": [],
+ "order": null,
+ "limit": null
+}</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>VERIFIED: ir, columns, entity, joins, periods, measure, grouping, filters, limit, guard, plan, recompute</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="247" customHeight="1">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Compare the total amount of loans granted in Q1-Q3 of 1995 with Q1-Q3 of 1998.</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>SELECT
+  loan_year,
+  SUM(amount) AS total_loan_amount,
+  COUNT(*) AS loan_count
+FROM ai.loan
+WHERE
+  (
+    loan_date &gt;= CAST('1995-01-01' AS DATE)
+    AND loan_date &lt; CAST('1995-10-01' AS DATE)
+  )
+  OR (
+    loan_date &gt;= CAST('1998-01-01' AS DATE)
+    AND loan_date &lt; CAST('1998-10-01' AS DATE)
+  )
+GROUP BY
+  loan_year
+ORDER BY
+  loan_year
+LIMIT 10000</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>loan_year=1995 | total_loan_amount=9033564.0 | loan_count=63
+loan_year=1998 | total_loan_amount=21046932.0 | loan_count=132</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>year=1995 | loans=63 | total_amount=9033564.0
+year=1998 | loans=132 | total_amount=21046932.0</t>
+        </is>
+      </c>
+      <c r="F20" s="12" t="inlineStr">
+        <is>
+          <t>match</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>ai.loan is the entity for the certified total_loan_amount metric (sum of principal, grain loan_id), so no joins are needed and there is no fan-out. Each named year gets its own date range, Q1-Q3 meaning 1 January to 30 September as half-open ranges on loan_date, and the result is grouped by loan_year to give one row per year for comparison.
+- Q1-Q3 means calendar quarters, 1 January to 30 September of each year.
+- 'Total amount of loans' means the principal granted (sum of amount), not monthly_payment * duration_months.
+- Loan counts are returned beside the totals so the comparison shows how many loans each total covers.
+- Results cover only the clients the caller is entitled to see, so the totals describe that portfolio.</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>{
+ "metric": "total_loan_amount",
+ "entity": "ai.loan",
+ "counting_grain": "loan_id",
+ "time": {
+  "column": "loan_date",
+  "periods": [
+   {
+    "from": "1995-01-01",
+    "to": "1995-10-01"
+   },
+   {
+    "from": "1998-01-01",
+    "to": "1998-10-01"
+   }
+  ]
+ },
+ "group_by": [
+  "loan_year"
+ ],
+ "filters": [],
+ "order": null,
+ "limit": null
+}</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>VERIFIED: ir, columns, entity, joins, periods, measure, grouping, filters, limit, guard, plan, recompute</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="117" customHeight="1">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>E3</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>How many new accounts were opened in Q1 1996?</t>
+        </is>
+      </c>
+      <c r="C21" s="9" t="inlineStr">
+        <is>
+          <t>SELECT
+  COUNT(*) AS account_count
+FROM ai.account
+WHERE
+  open_date &gt;= CAST('1996-01-01' AS DATE)
+  AND open_date &lt; CAST('1996-04-01' AS DATE)
+LIMIT 10000</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>account_count=334</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>new_accounts=334</t>
+        </is>
+      </c>
+      <c r="F21" s="12" t="inlineStr">
+        <is>
+          <t>match</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>A 'new account' is an account whose open_date falls in the period, so I used the certified account_count metric on ai.account, which has one row per account and needs no join. Q1 is read as the calendar quarter, January to March 1996, filtered with a half-open range on open_date. I did not use a loan or transaction date column.
+- Q1 1996 means the calendar quarter 1 January to 31 March 1996.
+- The count covers only the accounts the caller is entitled to see, because results are filtered by the database policy.</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>{
+ "metric": "account_count",
+ "entity": "ai.account",
+ "counting_grain": "account_id",
+ "time": {
+  "column": "open_date",
+  "periods": [
+   {
+    "from": "1996-01-01",
+    "to": "1996-04-01"
+   }
+  ]
+ },
+ "group_by": [],
+ "filters": [],
+ "order": null,
+ "limit": null
+}</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>VERIFIED: ir, columns, entity, joins, periods, measure, grouping, filters, limit, guard, plan, recompute</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="247" customHeight="1">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>E4</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>How many loans were granted per quarter in 1996?</t>
+        </is>
+      </c>
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>SELECT
+  c.quarter AS quarter,
+  COUNT(l.loan_id) AS loan_count
+FROM (
+  SELECT DISTINCT
+    quarter
+  FROM ai.calendar
+  WHERE
+    date_key &gt;= CAST('1996-01-01' AS DATE) AND date_key &lt; CAST('1997-01-01' AS DATE)
+) AS c
+LEFT JOIN ai.loan AS l
+  ON EXTRACT(QUARTER FROM l.loan_date) = c.quarter
+  AND l.loan_date &gt;= CAST('1996-01-01' AS DATE)
+  AND l.loan_date &lt; CAST('1997-01-01' AS DATE)
+GROUP BY
+  c.quarter
+ORDER BY
+  c.quarter
+LIMIT 10000</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>quarter=1 | loan_count=20
+quarter=2 | loan_count=23
+quarter=3 | loan_count=39
+quarter=4 | loan_count=35</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>quarter=1 | loans=20 | total_amount=2907960.0
+quarter=2 | loans=23 | total_amount=4103220.0
+quarter=3 | loans=39 | total_amount=5196876.0
+quarter=4 | loans=35 | total_amount=6109620.0</t>
+        </is>
+      </c>
+      <c r="F22" s="12" t="inlineStr">
+        <is>
+          <t>match</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>ai.loan is the pre-joined loan entity and loan_count is the certified metric, counted at loan_id grain and filtered on loan_date with a half-open 1996 range. Quarters come from a calendar-derived list left-joined to loans so a quarter with no loans returns 0 rather than being omitted, and there is no join to a many-side table so nothing fans out.
+- Quarters are calendar quarters (Q1 = Jan-Mar ... Q4 = Oct-Dec) of 1996, based on loan_date.
+- Counts cover only the loans the caller is entitled to see, so they describe the caller's portfolio, not necessarily the whole bank.</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>{
+ "metric": "loan_count",
+ "entity": "ai.loan",
+ "counting_grain": "loan_id",
+ "time": {
+  "column": "loan_date",
+  "periods": [
+   {
+    "from": "1996-01-01",
+    "to": "1997-01-01"
+   }
+  ]
+ },
+ "group_by": [
+  "quarter"
+ ],
+ "filters": [],
+ "order": null,
+ "limit": null
+}</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>VERIFIED: ir, columns, entity, joins, periods, measure, grouping, filters, limit, guard, plan, recompute</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="13" t="inlineStr">
+        <is>
+          <t>Evaluation tally</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>match: 4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A2:I2"/>
+  <mergeCells count="2">
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A18:K18"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3593,7 +4234,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E49"/>
+  <dimension ref="A1:E52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -3903,7 +4544,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>A calendar-year difference (year(loan) - year(birth)) reports ages roughly 0.5 years higher.</t>
+          <t>Truncating to completed years (date_part('year', age(loan, birth))) reports ages about 0.5 years lower (36.59 vs 37.07 for status A). A calendar-year difference (year(loan) - year(birth)) lands within 0.11 years of the exact average per status, but is wrong for any individual loan. (Corrected 2026-10-28: an earlier version said the calendar-year difference reads 0.5 years high; measured, it does not.)</t>
         </is>
       </c>
     </row>
@@ -4001,17 +4642,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>The balance at 1998-12-31 is the balance after the last posting on or before that date, from core.fact_account_month_end_balance, with ties on a date broken by the highest trans_id.</t>
+          <t>The balance at 1998-12-31 is the balance after the last posting on or before that date, from core.fact_account_month_end_balance. When several postings share the last date, the closing one is the end of that day's running-balance chain (each posting starts at balance_after - signed_amount); where the chain cannot order them, the lowest trans_id among the chain ends is used and the row is marked closing_basis = 'ambiguous' (D028).</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>trans_id is not chronological within a day, so a tie-break is unavoidable; it is documented and applied identically in the reference SQL, in the model and in the semantic layer.</t>
+          <t>The source has no time of day and trans_id is not chronological; the running balance is the only recorded evidence of order. Where the chain resolves the order, lowest id agrees with it 96.9% of the time and highest id 0.4%.</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>183 accounts have several postings on their latest date (rule CON_INTRADAY_ORDER_AMBIGUOUS, warn), so for those the closing balance is a documented choice rather than a fact.</t>
+          <t>183 accounts have several postings on their latest date: 141 are resolved by the chain, 42 remain ambiguous. Before D028 the highest trans_id was used, which put Q9 at 43,808.94 instead of 43,810.47.</t>
         </is>
       </c>
     </row>
@@ -4072,808 +4713,889 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>A17</t>
+          <t>A47</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Dates</t>
+          <t>E1 (gender of loans)</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>A two-digit source year is always 19xx.</t>
+          <t>"Male or female loans" counts loans, once each, grouped by the gender of the loan's account owner (ai.loan.owner_gender, i.e. core.dim_client.gender through the OWNER disposition). Pending business confirmation.</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>The dataset runs 1993-1998 and was published in 1999; there is no 20xx data.</t>
+          <t>Gender is an attribute of a client only (ai.client.gender); ai.loan and ai.account_owner carry it as owner_gender. A loan has no borrower of its own in the source; it reaches a person through its account, and A5/A11 already attribute loans to the owner. Every account has exactly one owner, so the join cannot repeat a loan.</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>A 20xx reading would move dates out of the validity window, which rule VAL_DATE_OUT_OF_RANGE would block -- so the assumption fails loudly rather than silently.</t>
+          <t>Q1 1995: 28 loans, 18 male-owned and 10 female-owned. Counting every client on the account (owners and disponents) counts loan-client pairs, not loans: 34 pairs, because 6 loans have a disponent of the other gender, so the two groups would overlap. The verifier refuses that join path for loan_count unless the metric is redefined.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>A18</t>
+          <t>A48</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Gender</t>
+          <t>E1-E4 (quarters)</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>birth_number encodes sex as month + 50 for women, and that is the only available source for gender.</t>
+          <t>"Q1"-"Q4" in a question are calendar quarters (Jan-Mar, Apr-Jun, Jul-Sep, Oct-Dec), written as half-open date ranges, and a comparison across periods returns one row per period. Q1-Q10 in the context pack only label the reference questions. Pending business confirmation.</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Documented with the dataset; CON_GENDER_MATCHES_BIRTH_NUMBER checks the decode against the raw digits on every run.</t>
+          <t>The book has no fiscal calendar and nothing in the source defines one. One row per period is what the verifier can check against the IR and what the evaluator compares.</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Q8 is entirely built on it. The rule turns a decoder regression into a build failure.</t>
+          <t>A fiscal year starting in another month moves every quarter boundary; it would be one change to ai.calendar and the IR periods, and the day-by-day period check would then enforce the new boundaries. A pivoted answer (one column per period) is refused today and would need the verifier extended.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>A19</t>
+          <t>A49</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Currency</t>
+          <t>Q5 (interest)</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>All amounts are in the same currency (CZK) and no conversion is needed.</t>
+          <t>Bank-credited interest (category_code = 'UROK', 48,788 credits in 1997) counts as incoming money. Pending business confirmation.</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Single-country dataset from one bank; no currency column exists.</t>
+          <t>A7 defines incoming as every PRIJEM credit, and interest is one. The previous audit listed this as an open decision; nothing in the source settles it.</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>If a second currency appeared, every sum (Q2, Q4, Q5, Q9) would be adding unlike units. There is no rule that could detect it from this schema, which is why it is written down.</t>
+          <t>Measured for 1997: interest is 7,372,897.70 of 864,692,326.70 CZK incoming (0.85%). Excluding it lowers every district's total by about that share and leaves the top-10 order unchanged.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>A20</t>
+          <t>A17</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Rounding</t>
+          <t>Dates</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Source amounts carry one decimal place, and the per-account balance chain is therefore reconciled with a tolerance (1 CZK rounding band, 100 CZK materiality band) rather than exactly.</t>
+          <t>A two-digit source year is always 19xx.</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Measured: every one of 1,056,320 amounts has a zero in the second decimal.</t>
+          <t>The dataset runs 1993-1998 and was published in 1999; there is no 20xx data.</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>631 of 4,500 accounts reconcile exactly, 4,364 within 1 CZK, 55 are off by more than 100 CZK. Without the bands the rule would report 3,869 "defects" and hide the 55 that matter.</t>
+          <t>A 20xx reading would move dates out of the validity window, which rule VAL_DATE_OUT_OF_RANGE would block -- so the assumption fails loudly rather than silently.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>A21</t>
+          <t>A18</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Entitlements</t>
+          <t>Gender</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>A user entitled to a client sees that client, the accounts that client owns, and everything hanging off those accounts. A disponent relationship does not grant the portfolio holder access to the account.</t>
+          <t>birth_number encodes sex as month + 50 for women, and that is the only available source for gender.</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>"Each user sees only rows for their own clients": ownership is the relationship a relationship manager is accountable for.</t>
+          <t>Documented with the dataset; CON_GENDER_MATCHES_BIRTH_NUMBER checks the decode against the raw digits on every run.</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Including disponent relationships would widen every portfolio; sec.portfolio_client plus the policy predicate is where that choice is changed, and it is one SQL predicate, not a model change.</t>
+          <t>Q8 is entirely built on it. The rule turns a decoder regression into a build failure.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>A22</t>
+          <t>A19</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Entitlements</t>
+          <t>Currency</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Reference data (dim_district, dim_date, ref_codes) is not entitlement filtered.</t>
+          <t>All amounts are in the same currency (CZK) and no conversion is needed.</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>They contain no client information, and filtering them would break every group-by for every user.</t>
+          <t>Single-country dataset from one bank; no currency column exists.</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>If districts were considered sensitive, the policy would be added to those tables too; nothing else in the design changes.</t>
+          <t>If a second currency appeared, every sum (Q2, Q4, Q5, Q9) would be adding unlike units. There is no rule that could detect it from this schema, which is why it is written down.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>A23</t>
+          <t>A20</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Data copy</t>
+          <t>Rounding</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>The public Berka copy is the primary dataset, because data/raw/provided/ is empty. Its row counts match the published reference exactly, so it carries no injected defects.</t>
+          <t>Source amounts carry one decimal place, and the per-account balance chain is therefore reconciled with a tolerance (1 CZK rounding band, 100 CZK materiality band) rather than exactly.</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>No bank-supplied copy was received (decision point HD1).</t>
+          <t>Measured: every one of 1,056,320 amounts has a zero in the second decimal.</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>On the bank's copy the counts would differ, REC_ROWCOUNT_RAW_TO_STG and REC_LOAN_STATUS_DISTRIBUTION would fire, and the same 123 rules would run unchanged against data/raw/provided/.</t>
+          <t>637 of 4,500 accounts reconcile exactly, 4,416 within 1 CZK, 14 are off by more than 100 CZK (largest 488.30). Without the bands the rule would report 3,863 "defects" and hide the 14 that matter. (Before D028 the figures were 631 / 4,364 / 55: 41 of the 55 came from reading the wrong closing posting, not from the source.)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>A24</t>
+          <t>A21</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>LLM</t>
+          <t>Entitlements</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>The LLM is treated as an untrusted query author: it sees the semantic layer and the question, never the database, and its SQL is parsed and rewritten before execution.</t>
+          <t>A user entitled to a client sees that client, the accounts that client owns, and everything hanging off those accounts. A disponent relationship does not grant the portfolio holder access to the account.</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>It is the only assumption under which "an LLM-generated query cannot bypass the filter" can be true.</t>
+          <t>"Each user sees only rows for their own clients": ownership is the relationship a relationship manager is accountable for.</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>If the model were trusted, the entitlement filter would have to live in the prompt -- which is a request, not a control.</t>
+          <t>Including disponent relationships would widen every portfolio; sec.portfolio_client plus the policy predicate is where that choice is changed, and it is one SQL predicate, not a model change.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>A25</t>
+          <t>A22</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>C03</t>
+          <t>Entitlements</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>The placeholder list ('', '?', 'NA', 'N/A', 'NULL', '-', 'unknown') is the complete set of ways this source writes "missing".</t>
+          <t>Reference data (dim_district, dim_date, ref_codes) is not entitlement filtered.</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Derived by profiling every text column, not assumed up front; the profiler reports the full distinct-value distribution per column and no other placeholder-shaped value appeared.</t>
+          <t>They contain no client information, and filtering them would break every group-by for every user.</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>An eighth spelling would be counted as a real value, overstating completeness for that column. It would not corrupt anything downstream, and the profile report is where it would show up. Low risk, cheap to extend: one tuple in src/config.NULL_PLACEHOLDERS.</t>
+          <t>If districts were considered sensitive, the policy would be added to those tables too; nothing else in the design changes.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>A26</t>
+          <t>A23</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>C03, C09</t>
+          <t>Data copy</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>A NULL after cleaning means "the source did not record this", never "the pipeline lost it".</t>
+          <t>The public Berka copy is the primary dataset, because data/raw/provided/ is empty. Its row counts match the published reference exactly, so it carries no injected defects.</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Every value the cleaning dropped or changed is kept in a &lt;column&gt;_raw column and listed in _conversion_notes, so the two cases are distinguishable by construction.</t>
+          <t>No bank-supplied copy was received (decision point HD1).</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>This is the assumption the whole ledger exists to make checkable. If it were false, every completeness number would be measuring the loader rather than the source.</t>
+          <t>On the bank's copy the counts would differ, REC_ROWCOUNT_RAW_TO_STG and REC_LOAN_STATUS_DISTRIBUTION would fire, and the same 123 rules would run unchanged against data/raw/provided/.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>A27</t>
+          <t>A24</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>C09</t>
+          <t>LLM</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>operation_code IS NULL on a transaction means a bank-generated posting, not a missing value.</t>
+          <t>The LLM is treated as an untrusted query author: it sees the semantic layer and the question, never the database, and its SQL is parsed and rewritten before execution.</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Measured: all 183,114 rows with no operation carry k_symbol = UROK (interest credited), and no other category has a NULL operation. The bank books interest without a customer-facing operation.</t>
+          <t>It is the only assumption under which "an LLM-generated query cannot bypass the filter" can be true.</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>If some of those NULLs were genuinely missing data, the completeness rule on that column would have to be warn rather than info, and "transactions by operation" would be understating one category. The measurement is re-run every build, so a mixed population would show up as UROK no longer being the only value.</t>
+          <t>If the model were trusted, the entitlement filter would have to live in the prompt -- which is a request, not a control.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>A28</t>
+          <t>A25</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>C09, D017</t>
+          <t>C03</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>The code sets are open: the source may contain a code the catalogue does not know, and the right response is to fail the build rather than guess a label.</t>
+          <t>The placeholder list ('', '?', 'NA', 'N/A', 'NULL', '-', 'unknown') is the complete set of ways this source writes "missing".</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>It already happened. LEASING appeared on 341 standing orders and was not in the map; because the catalogue check did not cover that table, nothing failed and the rows shipped unlabelled.</t>
+          <t>Derived by profiling every text column, not assumed up front; the profiler reports the full distinct-value distribution per column and no other placeholder-shaped value appeared.</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>The assumption now has teeth: check_codes_against_staging covers every coded column and tests/test_dq.py::test_every_present_code_resolves_to_a_label fails if any staged row carries a code with no label. A new code stops a build, which is the intended cost.</t>
+          <t>An eighth spelling would be counted as a real value, overstating completeness for that column. It would not corrupt anything downstream, and the profile report is where it would show up. Low risk, cheap to extend: one tuple in src/config.NULL_PLACEHOLDERS.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>A29</t>
+          <t>A26</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>C10</t>
+          <t>C03, C09</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>PRIJEM is the only credit type; VYDAJ and VYBER are both debits.</t>
+          <t>A NULL after cleaning means "the source did not record this", never "the pipeline lost it".</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Documented with the dataset, and consistent with the reported running balance: the balance chain reconciles for 4,364 of 4,500 accounts under this sign convention and would reconcile for almost none under any other.</t>
+          <t>Every value the cleaning dropped or changed is kept in a &lt;column&gt;_raw column and listed in _conversion_notes, so the two cases are distinguishable by construction.</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Every monetary answer that nets or directs money (Q5, Q9) depends on it. The balance reconciliation rule is the check: a wrong sign convention would make it fail at scale rather than for 55 accounts.</t>
+          <t>This is the assumption the whole ledger exists to make checkable. If it were false, every completeness number would be measuring the loader rather than the source.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>A30</t>
+          <t>A27</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>C10, C20</t>
+          <t>C09</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>balance_after as reported by the bank is authoritative; the pipeline never recomputes it from the amounts.</t>
+          <t>operation_code IS NULL on a transaction means a bank-generated posting, not a missing value.</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>It is the bank's own record of the account state after the posting. Recomputing would substitute this pipeline's arithmetic for the bank's ledger.</t>
+          <t>Measured: all 183,114 rows with no operation carry k_symbol = UROK (interest credited), and no other category has a NULL operation. The bank books interest without a customer-facing operation.</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>The 55 accounts whose chain does not reconcile beyond 100 CZK are reported as a defect rather than corrected (D013). If the bank's balances were known to be unreliable, the derived balance would become the published one and those 55 would become silent.</t>
+          <t>If some of those NULLs were genuinely missing data, the completeness rule on that column would have to be warn rather than info, and "transactions by operation" would be understating one category. The measurement is re-run every build, so a mixed population would show up as UROK no longer being the only value.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>A31</t>
+          <t>A28</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>C19, C20</t>
+          <t>C09, D017</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>The extract is a point-in-time snapshot with no history: no attribute of a client, account or district changes over time within it.</t>
+          <t>The code sets are open: the source may contain a code the catalogue does not know, and the right response is to fail the build rather than guess a label.</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>There is no effective-date column anywhere in the eight files, and no table carries two versions of the same key.</t>
+          <t>It already happened. LEASING appeared on 341 standing orders and was not in the map; because the catalogue check did not cover that table, nothing failed and the rows shipped unlabelled.</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>No slowly changing dimensions are needed, which is why dim_client and dim_district are plain. A feed with history would need SCD2 on at least district attributes, since the 1995/1996 socio-economic columns are already two snapshots flattened into one row.</t>
+          <t>The assumption now has teeth: check_codes_against_staging covers every coded column and tests/test_dq.py::test_every_present_code_resolves_to_a_label fails if any staged row carries a code with no label. A new code stops a build, which is the intended cost.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>A32</t>
+          <t>A29</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>C19</t>
+          <t>C10</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>The dataset window is 1993-01-01 to 1998-12-31, and dim_date is generated to exactly that span.</t>
+          <t>PRIJEM is the only credit type; VYDAJ and VYBER are both debits.</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Measured from the data: the earliest and latest transaction dates are exactly those two days.</t>
+          <t>Documented with the dataset, and consistent with the reported running balance: the balance chain reconciles within 1 CZK for 4,416 of 4,500 accounts under this sign convention and would reconcile for almost none under any other.</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>A date outside the window would not join to dim_date and would drop out of any date-driven aggregate. VAL_DATE_OUT_OF_RANGE is the rule that makes that fail loudly rather than quietly.</t>
+          <t>Every monetary answer that nets or directs money (Q5, Q9) depends on it. The balance reconciliation rule is the check: a wrong sign convention would make it fail at scale rather than for 14 accounts.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>A33</t>
+          <t>A30</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>C16</t>
+          <t>C10, C20</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Row order within a source file carries no meaning; the only ordering is by the date and key columns.</t>
+          <t>balance_after as reported by the bank is authoritative; the pipeline never recomputes it from the amounts.</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>The files are flat extracts with no sequence column beyond the surrogate ids, and trans_id is demonstrably not chronological within a day (CON_INTRADAY_ORDER_AMBIGUOUS, 183 accounts).</t>
+          <t>It is the bank's own record of the account state after the posting. Recomputing would substitute this pipeline's arithmetic for the bank's ledger.</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>If file order were the true posting order, the Q9 tie-break would have a better answer available and those 183 accounts would stop being ambiguous. _source_row is retained on every row, so that reading could be tested without a reload.</t>
+          <t>The 14 accounts whose chain does not reconcile beyond 100 CZK are reported as a defect rather than corrected (D013). If the bank's balances were known to be unreliable, the derived balance would become the published one and those 14 would become silent. The same balances are also what orders same-day postings (D028), so this assumption now carries Q9's closing posting as well.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>A34</t>
+          <t>A31</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Identity</t>
+          <t>C19, C20</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>A self-service customer authenticates as their own database login role, and that role is never shared, pooled or re-pointed.</t>
+          <t>The extract is a point-in-time snapshot with no history: no attribute of a client, account or district changes over time within it.</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Same reasoning as A21/D009 for staff: session_user cannot be changed by any statement the caller or an LLM emits, because changing it needs a password neither ever sees.</t>
+          <t>There is no effective-date column anywhere in the eight files, and no table carries two versions of the same key.</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>This is the load-bearing assumption of the whole privacy claim. If customer logins were pooled behind one shared role, the entitlement would resolve to that shared role and every customer would see every other customer's data. Connection pooling is therefore named in the DDR as the first thing that must be redesigned, not quietly added.</t>
+          <t>No slowly changing dimensions are needed, which is why dim_client and dim_district are plain. A feed with history would need SCD2 on at least district attributes, since the 1995/1996 socio-economic columns are already two snapshots flattened into one row.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>A35</t>
+          <t>A32</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Identity</t>
+          <t>C19</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>A customer is entitled to exactly the client record that sec.app_user.subject_client_id names, and the mapping from a real person to that client id is correct and is made outside this system.</t>
+          <t>The dataset window is 1993-01-01 to 1998-12-31, and dim_date is generated to exactly that span.</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>This dataset has no identity documents, no logins and no names; the mapping from "the person at the counter" to client_id is the bank's KYC process, not a data-product concern.</t>
+          <t>Measured from the data: the earliest and latest transaction dates are exactly those two days.</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>The product enforces the mapping it is given. A wrong mapping shows the wrong person's data with the full force of a correct-looking entitlement, and nothing in this build could detect it. In a real deployment the insert into sec.app_user is the output of an identity-proofing process and should be auditable on that basis.</t>
+          <t>A date outside the window would not join to dim_date and would drop out of any date-driven aggregate. VAL_DATE_OUT_OF_RANGE is the rule that makes that fail loudly rather than quietly.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>A36</t>
+          <t>A33</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Identity</t>
+          <t>C16</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>A customer sees the accounts they own, not the accounts they may merely operate as a disponent.</t>
+          <t>Row order within a source file carries no meaning; the only ordering is by the date and key columns.</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Consistency with A21 and the safer default for a privacy boundary (D022).</t>
+          <t>The files are flat extracts with no sequence column beyond the surrogate ids, and trans_id is demonstrably not chronological within a day (CON_INTRADAY_ORDER_AMBIGUOUS, 183 accounts).</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>869 clients hold a disponent relationship. Under the other reading each of them would additionally see that account and its postings. It is one predicate in sec.v_my_accounts and it is a business decision, not a technical one.</t>
+          <t>The running balance orders 141 of those 183 (D028); 42 remain ambiguous. If file order were the true posting order, those 42 would have an answer too. _source_row is retained on every row, so that reading could be tested without a reload.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>A37</t>
+          <t>A34</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Privacy</t>
+          <t>Identity</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Reference data (districts, calendar, code catalogue) is not sensitive, so a customer may read all 77 districts even though they belong to one.</t>
+          <t>A self-service customer authenticates as their own database login role, and that role is never shared, pooled or re-pointed.</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Same as A22: filtering it would break every group-by, and a district list reveals nothing about any client.</t>
+          <t>Same reasoning as A21/D009 for staff: session_user cannot be changed by any statement the caller or an LLM emits, because changing it needs a password neither ever sees.</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>If district-level data were considered identifying in combination with other attributes, the policy would extend to it. Nothing else in the design changes.</t>
+          <t>This is the load-bearing assumption of the whole privacy claim. If customer logins were pooled behind one shared role, the entitlement would resolve to that shared role and every customer would see every other customer's data. Connection pooling is therefore named in the DDR as the first thing that must be redesigned, not quietly added.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>A38</t>
+          <t>A35</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Privacy</t>
+          <t>Identity</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>No read audit is required for this submission.</t>
+          <t>A customer is entitled to exactly the client record that sec.app_user.subject_client_id names, and the mapping from a real person to that client id is correct and is made outside this system.</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>The brief asks who *can* see what, not what was actually read.</t>
+          <t>This dataset has no identity documents, no logins and no names; the mapping from "the person at the counter" to client_id is the bank's KYC process, not a data-product concern.</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>For a real bank this is a regulatory gap, not a simplification. It is listed in the worked example's limits and in the build review as the largest missing control.</t>
+          <t>The product enforces the mapping it is given. A wrong mapping shows the wrong person's data with the full force of a correct-looking entitlement, and nothing in this build could detect it. In a real deployment the insert into sec.app_user is the output of an identity-proofing process and should be auditable on that basis.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>A39</t>
+          <t>A36 (superseded by A39 / D023)</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Access</t>
+          <t>Identity</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>A customer may see every account they are authorised to OPERATE, including accounts they do not own.</t>
+          <t>A customer sees the accounts they own, not the accounts they may merely operate as a disponent.</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>What the bank tells its customers their app will show. Supersedes A36, which narrowed them to ownership; the decision was taken to the business reading and settled (D023).</t>
+          <t>Consistency with A21 and the safer default for a privacy boundary (D022).</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>869 clients hold a disposition on an account they do not own. Under the narrow reading each of them sees one fewer account. It is one branch in sec.v_access_grant.</t>
+          <t>869 clients hold a disponent relationship. Under the other reading each of them would additionally see that account and its postings. It is one predicate in sec.v_my_accounts and it is a business decision, not a technical one.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>A40</t>
+          <t>A37</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Access</t>
+          <t>Privacy</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>A disposition grants the ACCOUNT and nothing else -- not the owner's client record, not their other accounts.</t>
+          <t>Reference data (districts, calendar, code catalogue) is not sensitive, so a customer may read all 77 districts even though they belong to one.</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Authorising someone to pay a bill from your account is not authorising them to read you. Nobody signing that arrangement would expect otherwise.</t>
+          <t>Same as A22: filtering it would break every group-by, and a district list reveals nothing about any client.</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>If a disposition granted the owning client instead, every disponent would see their co-holder's full customer record. This is the single most consequential line in the access model, and it is tested by name.</t>
+          <t>If district-level data were considered identifying in combination with other attributes, the policy would extend to it. Nothing else in the design changes.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>A41</t>
+          <t>A38</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Access</t>
+          <t>Privacy</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>A staff portfolio grants view and never operate.</t>
+          <t>No read audit is required for this submission.</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Being accountable for a client is not authority to move their money.</t>
+          <t>The brief asks who *can* see what, not what was actually read.</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Nothing acts on operate in this read-only product, so the distinction costs nothing today and cannot be recovered later if it is dropped now. A test pins it.</t>
+          <t>For a real bank this is a regulatory gap, not a simplification. It is listed in the worked example's limits and in the build review as the largest missing control.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>A42</t>
+          <t>A39</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Identity</t>
+          <t>Access</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>An opaque client_ref is sufficient protection for an identifier that appears in a URL or on a statement; it does not need to be rotated per session.</t>
+          <t>A customer may see every account they are authorised to OPERATE, including accounts they do not own.</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>It is unguessable without the salt, and row level security stops access regardless. The reference prevents enumeration and correlation, not access.</t>
+          <t>What the bank tells its customers their app will show. Supersedes A36, which narrowed them to ownership; the decision was taken to the business reading and settled (D023).</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>If a reference leaked in bulk, rebuilding under a new salt reissues all of them. Per-session identifiers would be stronger and would make every support conversation impossible.</t>
+          <t>869 clients hold a disposition on an account they do not own. Under the narrow reading each of them sees one fewer account. It is one branch in sec.v_access_grant.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>A43</t>
+          <t>A40</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Authentication</t>
+          <t>Access</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>A time-based one-time code is an adequate second factor for this demonstration.</t>
+          <t>A disposition grants the ACCOUNT and nothing else -- not the owner's client record, not their other accounts.</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>It is the standard most people already have an app for, and it is verifiable offline against RFC 6238.</t>
+          <t>Authorising someone to pay a bill from your account is not authorising them to read you. Nobody signing that arrangement would expect otherwise.</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>TOTP is phishable in real time: a victim relaying a live code to an attacker defeats it. A deployment handling real money should prefer a phishing-resistant factor (WebAuthn/passkeys). The session model here would not change; only the factor would.</t>
+          <t>If a disposition granted the owning client instead, every disponent would see their co-holder's full customer record. This is the single most consequential line in the access model, and it is tested by name.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>A44</t>
+          <t>A41</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Authentication</t>
+          <t>Access</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Storing TOTP shared secrets in a recoverable form is acceptable here.</t>
+          <t>A staff portfolio grants view and never operate.</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Verification requires the secret, so it cannot be hashed.</t>
+          <t>Being accountable for a client is not authority to move their money.</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>sec.auth_factor.secret is the most sensitive column in the schema. A real deployment encrypts it with a key held outside the database, so that a dump of the data is not a dump of everyone's second factor.</t>
+          <t>Nothing acts on operate in this read-only product, so the distinction costs nothing today and cannot be recovered later if it is dropped now. A test pins it.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>A45</t>
+          <t>A42</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Authentication</t>
+          <t>Identity</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Binding a session to (db_role, pg_backend_pid) is sufficient to stop replay.</t>
+          <t>An opaque client_ref is sufficient protection for an identifier that appears in a URL or on a statement; it does not need to be rotated per session.</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>A stolen session id is useless on a different connection, and the holder cannot forge session_user either.</t>
+          <t>It is unguessable without the salt, and row level security stops access regardless. The reference prevents enumeration and correlation, not access.</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Backend pids are reused after wraparound. A replay would need the same pid, the same role and the session still inside its 30-minute window; the combination is thin but not impossible, and a production system would add the backend start time to the binding.</t>
+          <t>If a reference leaked in bulk, rebuilding under a new salt reissues all of them. Per-session identifiers would be stronger and would make every support conversation impossible.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
+          <t>A43</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>Authentication</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>A time-based one-time code is an adequate second factor for this demonstration.</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>It is the standard most people already have an app for, and it is verifiable offline against RFC 6238.</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>TOTP is phishable in real time: a victim relaying a live code to an attacker defeats it. A deployment handling real money should prefer a phishing-resistant factor (WebAuthn/passkeys). The session model here would not change; only the factor would.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>A44</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>Authentication</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>Storing TOTP shared secrets in a recoverable form is acceptable here.</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>Verification requires the secret, so it cannot be hashed.</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>sec.auth_factor.secret is the most sensitive column in the schema. A real deployment encrypts it with a key held outside the database, so that a dump of the data is not a dump of everyone's second factor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>A45</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>Authentication</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>Binding a session to (db_role, pg_backend_pid) is sufficient to stop replay.</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>A stolen session id is useless on a different connection, and the holder cannot forge session_user either.</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>Backend pids are reused after wraparound. A replay would need the same pid, the same role and the session still inside its 30-minute window; the combination is thin but not impossible, and a production system would add the backend start time to the binding.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
           <t>A46</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
         <is>
           <t>Demo</t>
         </is>
       </c>
-      <c r="C49" s="2" t="inlineStr">
+      <c r="C52" s="2" t="inlineStr">
         <is>
           <t>Printing the one-time code in the demo console does not weaken the claims being demonstrated.</t>
         </is>
       </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>The control being shown is what the second factor *stops*, not where the code comes from; every other part of the path is the production one.</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>A system that can display your own second factor has one factor. It is marked as a demo affordance at every call site and is the first thing a deployment removes.</t>
         </is>
@@ -4890,7 +5612,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -4968,7 +5690,7 @@
           <t>(b) Put the project at the repository root.</t>
         </is>
       </c>
-      <c r="E5" s="14" t="inlineStr">
+      <c r="E5" s="15" t="inlineStr">
         <is>
           <t>The repository *is* the submission. A nested folder adds one path segment to every command in the README and buys nothing; make all from the clone root is what a reviewer will try first.</t>
         </is>
@@ -5000,7 +5722,7 @@
           <t>(c), with (a) as the preferred path when a daemon is present. scripts/db_up.sh tries docker compose first and falls back automatically.</t>
         </is>
       </c>
-      <c r="E6" s="14" t="inlineStr">
+      <c r="E6" s="15" t="inlineStr">
         <is>
           <t>DuckDB has no row level security, so option (b) would reduce Task 3 to prose and untested SQL -- the weakest possible answer to the one task that is purely about enforcement. The native cluster runs the identical DDL, identical policies and identical tests, so nothing about the submission is hypothetical.</t>
         </is>
@@ -5033,7 +5755,7 @@
           <t>(b) github.com/jlacko/berka-dataset, which ships the original eight *.asc files (semicolon separated, quoted headers) plus the original "Financial Data description.pdf".</t>
         </is>
       </c>
-      <c r="E7" s="14" t="inlineStr">
+      <c r="E7" s="15" t="inlineStr">
         <is>
           <t>The mirror is verifiable against published figures, which is what matters for trust: row counts came out at 4,500 accounts / 5,369 clients / 5,369 dispositions / 892 cards / 682 loans / 77 districts / 6,471 orders / 1,056,320 transactions -- every one an exact match to the reference counts in the brief's dataset. The files are the unmodified .asc originals, not a re-exported CSV with renamed columns, so no column mapping guesswork is needed.</t>
         </is>
@@ -5065,7 +5787,7 @@
           <t>(b) -- confirmed with the candidate at decision point HD1.</t>
         </is>
       </c>
-      <c r="E8" s="14" t="inlineStr">
+      <c r="E8" s="15" t="inlineStr">
         <is>
           <t>A rule that has never fired is not evidence of anything. The injector (sql/70_inject_defects.sql, seeded and deterministic) corrupts a copy of stg in schema inject with one defect per rule family, and tests/test_dq.py asserts that the matching rule catches each one. The certified answers to the 10 questions are still computed on the untouched data, and every injected row is labelled as injected everywhere it appears.</t>
         </is>
@@ -5097,7 +5819,7 @@
           <t>(c) -- confirmed with the candidate at decision point HD2. src/llm_client.py keeps all three behind one interface, so switching provider is one environment variable.</t>
         </is>
       </c>
-      <c r="E9" s="14" t="inlineStr">
+      <c r="E9" s="15" t="inlineStr">
         <is>
           <t>The point of the exercise is whether the *semantic layer* is good enough for a model to produce correct SQL. That needs a real model call. The CLI is invoked with --strict-mcp-config, an empty MCP config, an explicit system prompt and every tool disallowed, so the model has no database connection, no filesystem and no search: it sees only the rendered semantic context pack and the question, exactly like an API call would. Without that sandboxing the result would prove nothing, because an agent could simply go and read the tables.</t>
         </is>
@@ -5130,7 +5852,7 @@
           <t>(c). src/config.py holds the mapping; src/build_model.py publishes it as core.ref_codes; sql/30_core.sql joins that table for every label; the semantic layer renders its allowed-value lists from the same place. The staging layer additionally decodes labels inline while casting, which is a convenience copy -- so build_model.check_codes_against_staging asserts that staging's labels equal ref_codes, and that no code exists in the data that the catalogue does not publish.</t>
         </is>
       </c>
-      <c r="E10" s="14" t="inlineStr">
+      <c r="E10" s="15" t="inlineStr">
         <is>
           <t>The failure mode that matters is not duplication, it is *silent* duplication: two places disagreeing and nobody noticing until a report and a dashboard show different words for the same loan. A checked copy fails the build instead.</t>
         </is>
@@ -5162,7 +5884,7 @@
           <t>(b) Use the natural keys as primary keys.</t>
         </is>
       </c>
-      <c r="E11" s="14" t="inlineStr">
+      <c r="E11" s="15" t="inlineStr">
         <is>
           <t>Surrogate keys buy conformance across multiple source systems and the ability to track slowly changing dimensions. There is one source system here and a single extract with no history, so they would buy a join per dimension and nothing else. They also make every example query longer, which matters when the queries are written by an LLM reading a context pack.</t>
         </is>
@@ -5194,7 +5916,7 @@
           <t>dq.v_blocked and dq.v_row_flags filter target_schema = 'stg', and the comment in sql/00_schemas.sql says why the filter is load-bearing.</t>
         </is>
       </c>
-      <c r="E12" s="14" t="inlineStr">
+      <c r="E12" s="15" t="inlineStr">
         <is>
           <t>The first version of dq.v_blocked selected every block-severity quarantine row regardless of which schema it came from. Running the rule self-tests therefore made the *injected* defects exclude *real* rows from the data product: core.dim_district came out at 76 rows instead of 77, dim_account at 4,457 instead of 4,500, and 11,024 transactions lost their account. Nothing in the data was wrong; the control plane was.
 build_model verifies the declared foreign keys and grains after every build, and it failed with eight problems before any deliverable was produced.
@@ -5230,7 +5952,7 @@
 (ii).</t>
         </is>
       </c>
-      <c r="E13" s="14" t="inlineStr">
+      <c r="E13" s="15" t="inlineStr">
         <is>
           <t>(a) is not a control, it is a request: the thing being filtered is also the thing being asked to apply the filter. (b) is real, but it is defeated by one query shape nobody thought of, and the blast radius of a mistake is every user. (c) puts the predicate inside the plan of every statement on that connection. The LLM never holds the connection -- it emits text -- and the predicate is not in the text, so no rewriting of the text can remove it. tests/test_rls.py runs nine bypass attempts (switch role, read the base tables, read the raw layer, set a session variable, edit the entitlement tables, disable the policy, drop the policy, write, join outwards) and all nine fail.
 A GUC can be set by anything that can send SQL, so an entitlement resolved from one is exactly as strong as the guard in front of it -- and the guard is a Python function, which is a weaker place to stand than the engine. session_user cannot be re-pointed without a password the model never sees. tests/test_rls.py::test_setting_a_session_variable_does_not_change_visibility sets app.end_user to another user's name and shows the visible row count does not move.
@@ -5264,7 +5986,7 @@
           <t>Every view on the path from a consumer to a policy carries security_invoker = true, and tests/test_rls.py::test_every_view_between_the_consumer_and_the_policy_is_security_invoker reads pg_class.reloptions and fails if any of them does not. The one deliberate exception, ai.my_entitlement, is named in the test with its reason.</t>
         </is>
       </c>
-      <c r="E14" s="14" t="inlineStr">
+      <c r="E14" s="15" t="inlineStr">
         <is>
           <t>A PostgreSQL view normally reads its base tables with its *owner's* rights, and a table owner is exempt from its own policies. So ai.loan -- an invoker view -- read core.v_loan_enriched -- an owner view -- and the policy was evaluated as berka_owner. Measured on a user entitled to nothing: ai.loan returned all 682 loans and ai.account_owner all 4,500 accounts, while core.fact_loan correctly returned 0 for the same user in the same session. The base table was right and the view chain was wrong.
 This is the most useful thing in this submission to be asked about. The design was right, the DDL was one setting short, and the symptom was invisible from the owner's connection -- the only way to see it was to connect as a restricted user and count rows. That is why the entitlement claims here are backed by tests that authenticate as real low-privilege roles, rather than by a description of the policies.</t>
@@ -5298,7 +6020,7 @@
 Value-based: every (dimension, measure) pair in the reference answer must appear on some row of the model's answer within a relative tolerance of 1e-4, and for the three ranked questions the order is checked too.</t>
         </is>
       </c>
-      <c r="E15" s="14" t="inlineStr">
+      <c r="E15" s="15" t="inlineStr">
         <is>
           <t>On the first run Q6 scored mismatch. The model's counts were identical to the reference for all twelve months; it had labelled the months 1996-01 while the evaluator was looking for the integer 1. That was a defect in the evaluator, not in the answer, so the evaluator now accepts any published representation of a dimension (a month as 1996-01, 1 or January; a district by name or id). To keep that change from quietly becoming "loosen until it passes", tests/test_evaluate.py corrupts the recorded answers and asserts the evaluator rejects them: doubled measures, a reversed ranking, truncated rows, an empty result and a missing answer all fail, and True is not allowed to match a count of 1.
 An agent that can read the database or the repository would answer the questions by looking, and the exercise would measure the agent rather than the semantic layer. The recorded transcripts in llm_logs/ show permission_denials: [] and a single turn per question, which is what a pure completion looks like.
@@ -5333,7 +6055,7 @@
           <t>The model target runs src.build_security after src.build_model, so the ai views, the policies and the grants are restored by the same command that invalidated them.</t>
         </is>
       </c>
-      <c r="E16" s="14" t="inlineStr">
+      <c r="E16" s="15" t="inlineStr">
         <is>
           <t>A target that leaves the database in a state no other target expects is a trap for the next person -- and make all ordering would have hidden it, because entitlements runs after model there anyway. The failure only appeared when a single step was re-run, which is exactly how someone iterates.</t>
         </is>
@@ -5365,14 +6087,14 @@
           <t>(c) Type, normalise, decode and derive -- but never overwrite an observation -- and let a separately graded rule layer decide the consequence.</t>
         </is>
       </c>
-      <c r="E17" s="14" t="inlineStr">
+      <c r="E17" s="15" t="inlineStr">
         <is>
           <t>A repaired value is indistinguishable from an observed one a week later. That is tolerable in a model you train and throw away, and not tolerable in a bank's data product where someone will eventually reconcile a number against a statement. Dropping is worse: it silently changes every denominator. The chosen shape means that of the cleaning steps in the ledger, exactly one (C14, quarantine) removes a row from the product, it removed 1, and C21 proves the arithmetic on both rows and money.</t>
         </is>
       </c>
       <c r="F17" s="11" t="inlineStr">
         <is>
-          <t>The product carries known-bad rows with flags on them, so a consumer has to be willing to read a caveat. The 55 accounts whose balance chain does not reconcile are still in core, still answerable, and still marked -- which is the honest result, and also the one that costs the reader more attention than a quietly cleaned number would.</t>
+          <t>The product carries known-bad rows with flags on them, so a consumer has to be willing to read a caveat. The accounts whose balance chain does not reconcile (55 when this was written, 14 since D028) are still in core, still answerable, and still marked -- which is the honest result, and also the one that costs the reader more attention than a quietly cleaned number would.</t>
         </is>
       </c>
     </row>
@@ -5397,7 +6119,7 @@
           <t>(c), with the placeholder list in src/config.NULL_PLACEHOLDERS and mirrored by stg.norm_text.</t>
         </is>
       </c>
-      <c r="E18" s="14" t="inlineStr">
+      <c r="E18" s="15" t="inlineStr">
         <is>
           <t>Option (a) makes every completeness number wrong, because ? counts as a value. Option (b) makes the cleaning unfalsifiable. Option (c) costs two columns per affected table and leaves the step checkable: C03 measured 1,380 rows where a placeholder became NULL (1,379 standing orders with no category, and the one district), and each of them can still be read in its raw form.</t>
         </is>
@@ -5429,7 +6151,7 @@
           <t>(b), with the trailing clock time stripped before parsing, and a failed parse returning NULL rather than raising.</t>
         </is>
       </c>
-      <c r="E19" s="14" t="inlineStr">
+      <c r="E19" s="15" t="inlineStr">
         <is>
           <t>The dataset window is 1993-1998 and VAL_DATE_OUT_OF_RANGE fires if anything lands outside it, so the sliding window would add a rule for a case that cannot occur in this extract. The NULL-on-failure part matters more than the century: a cast that throws aborts the load and hides the defect it tripped over, which is precisely the value a quality report needs to see. C05 parsed 1,062,394 dates and C04 found 0 amounts that failed to cast.</t>
         </is>
@@ -5461,7 +6183,7 @@
           <t>(c) Decode it, keep the original, and publish a validity flag beside both.</t>
         </is>
       </c>
-      <c r="E20" s="14" t="inlineStr">
+      <c r="E20" s="15" t="inlineStr">
         <is>
           <t>Leaving it packed means every age question re-implements the decoding, and an LLM writing that arithmetic from a context pack will get the month offset wrong. Dropping the original removes the only evidence the decoding was right. C07 decoded 5,369 birth dates and C08 derived 5,369 genders, with birth_number_valid true for all of them -- so the derivation is complete on this extract, which is worth knowing precisely because it will not be true of the next one.</t>
         </is>
@@ -5493,7 +6215,7 @@
           <t>(c). The map lives in src/config.py, is published as core.ref_codes, and build_model.check_codes_against_staging compares the catalogue against every coded column.</t>
         </is>
       </c>
-      <c r="E21" s="14" t="inlineStr">
+      <c r="E21" s="15" t="inlineStr">
         <is>
           <t>Codes only, and the semantic layer has to carry a glossary the model may ignore. Labels only, and the join back to the source is gone. Both, from one place, and the redundancy becomes a test: if the inline label in staging disagrees with the catalogue, the build stops. C09 labelled 2,466,175 coded values against 28 published codes.
 Consequence, and the one this decision was actually written for. The check is only as good as its list of columns, and the first build's list had stg.trans.k_symbol_code in it but not stg."order".k_symbol_code. The code LEASING therefore sat on 341 standing orders with no English label through the entire first submission. Nothing failed: the profiler reported the code in dq/results/profile.md, and the only rule that noticed was the null-label completeness sweep, which reads as "this column is often empty" rather than "a cleaning step did not happen".
@@ -5527,7 +6249,7 @@
           <t>(c) Publish signed_amount computed once, with amount and type kept beside it.</t>
         </is>
       </c>
-      <c r="E22" s="14" t="inlineStr">
+      <c r="E22" s="15" t="inlineStr">
         <is>
           <t>This is the single most valuable cleaning step in the build for AI-readiness, and it is worth being plain about why. Every "net flow", "total out", "largest withdrawal" question turns on a CASE over two Czech words. A query that gets it wrong does not fail -- it returns a confident, plausible, wrong number, and the most likely way for that to happen is an LLM that saw VYDAJ in a context pack and did not see VYBER. Resolving it once in the data removes the failure mode rather than guarding against it. C10 signed 1,056,320 postings.</t>
         </is>
@@ -5546,7 +6268,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>A month-end balance is derived, with the tie-break written down</t>
+          <t>A month-end balance is derived, with the tie-break written down (tie-break superseded by D028)</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -5559,7 +6281,7 @@
           <t>(c): latest trans_date in the month, ties broken by highest trans_id, gaps carried forward with is_carried_forward and balance_as_of_month_end exposed.</t>
         </is>
       </c>
-      <c r="E23" s="14" t="inlineStr">
+      <c r="E23" s="15" t="inlineStr">
         <is>
           <t>(a) guarantees two answers to the same question. (b) makes "average closing balance" silently exclude quiet accounts, which biases it upward. (c) costs one pre-computed table and makes the ambiguity visible rather than arbitrary: C20 shows 558 month ends inherited from an earlier posting, each marked as such.</t>
         </is>
@@ -5591,7 +6313,7 @@
           <t>(c). sql/10_stg.sql states it as a contract: *nothing is filtered out here*.</t>
         </is>
       </c>
-      <c r="E24" s="14" t="inlineStr">
+      <c r="E24" s="15" t="inlineStr">
         <is>
           <t>A rule layer cannot report on rows it cannot see. If staging drops the duplicate transaction, the uniqueness rule has nothing to count and the defect report says the data is clean. Separating the two means the quality report describes the source rather than describing what survived the loader -- which is the difference between a data quality report and a data quality anecdote.</t>
         </is>
@@ -5623,7 +6345,7 @@
           <t>(b) Add subject_client_id to sec.app_user and resolve it in sec.v_my_clients alongside the portfolio path.</t>
         </is>
       </c>
-      <c r="E25" s="14" t="inlineStr">
+      <c r="E25" s="15" t="inlineStr">
         <is>
           <t>(c) is the option this project already rejected for relationship managers (D009) and it is worse here, not better: a self-service surface is the one most likely to face the open internet, so it is the last place the filter should live in application code. (a) is genuinely tempting -- zero schema change -- but it models a customer as a degenerate book, which means 5,369 portfolios of one row each, an administrative surface where a customer's "book" could be edited to contain somebody else, and a portfolio_client table whose rows mean two different things. (b) says what is true: this principal is that client. The cost is one column, one UNION and one check constraint.
 Consequence, and the claim worth testing. The seven row level security policies did not change, and neither did any consumer view. The policies ask sec.v_my_clients which clients the caller may see; for a customer the answer is one row, and no policy needs to know that customer logins exist. tests/test_rls.py::test_the_client_grain_added_no_policy pins both the policy count and the fact that no policy mentions subject_client_id.
@@ -5644,7 +6366,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>The customer's view is narrowed to ownership, matching the manager's</t>
+          <t>The customer's view is narrowed to ownership, matching the manager's (superseded by D023)</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -5657,7 +6379,7 @@
           <t>(a) Ownership only, identical to the staff rule.</t>
         </is>
       </c>
-      <c r="E26" s="14" t="inlineStr">
+      <c r="E26" s="15" t="inlineStr">
         <is>
           <t>(b) is arguably the better product: in a real bank, an account you are authorised to transact on appears in your app. But it means the two grains of principal resolve accounts by *different* rules, and a reviewer asking "why does a customer see more kinds of account than their manager" deserves a better answer than "it seemed friendlier". Narrower is also the safer default for a privacy boundary: the failure mode of (a) is a customer who cannot see something they should, which is a support ticket; the failure mode of (b), if the disponent join is ever wrong, is a customer seeing an account that is not theirs.</t>
         </is>
@@ -5689,7 +6411,7 @@
           <t>(b) Ownership plus disposition.</t>
         </is>
       </c>
-      <c r="E27" s="14" t="inlineStr">
+      <c r="E27" s="15" t="inlineStr">
         <is>
           <t>It is what the bank tells its customers their app will show, and the narrow reading produces a support ticket every time somebody cannot see an account they transact on daily. The safety argument for (a) was real but it is answered by *where* the right is granted rather than by withholding it -- see D024.</t>
         </is>
@@ -5721,7 +6443,7 @@
           <t>(b), and it is the most important line in the access model.</t>
         </is>
       </c>
-      <c r="E28" s="14" t="inlineStr">
+      <c r="E28" s="15" t="inlineStr">
         <is>
           <t>(a) would mean that authorising someone to pay a bill from your account lets them read *you*: your other accounts, your loans, your date of birth. That is not what the arrangement means, and nobody signing it would expect it. The right is over the account, so the grant is over the account.</t>
         </is>
@@ -5753,7 +6475,7 @@
           <t>(c): client_id for joins, client_ref (BRK-XXXX-XXXX, HMAC under a secret salt) to quote, account_ref (IBAN with real mod-97 check digits, fictional bank code) for the number a customer recognises.</t>
         </is>
       </c>
-      <c r="E29" s="14" t="inlineStr">
+      <c r="E29" s="15" t="inlineStr">
         <is>
           <t>(a) leaves an enumeration surface that costs nothing to remove: every guess is an access attempt the system must refuse rather than one never made. (b) would make every join and every policy predicate longer and slower for no gain, because the internal key is never exposed anyway. (c) separates the identifier used for plumbing from the identifier used for people, and the semantic layer tells the model which is which.</t>
         </is>
@@ -5785,7 +6507,7 @@
           <t>(c) Enforce it in the database: no verified session, no rows.</t>
         </is>
       </c>
-      <c r="E30" s="14" t="inlineStr">
+      <c r="E30" s="15" t="inlineStr">
         <is>
           <t>(a) is where most real systems put it, and it is a defensible production architecture -- but it makes the control a property of the application rather than of the data, which is the same mistake this project rejected for entitlements in D009. (b) is a diagram, not a control. (c) makes the claim testable in the only way that means anything: hold the correct password, present no second factor, and read nothing. That is asserted for all eight principals across seven consumer views in tests/test_auth.py.
 Reason for the shape, which is the subtle part. Identity still comes from session_user, which no statement can forge. The session token is a *second* thing, and a bearer secret, so it is bound to pg_backend_pid(): a copied token is useless on another connection, and one user completing a login does not authorise every other connection open as the same role. The session check is ANDed over the whole of sec.v_my_clients rather than inside one branch, so a branch added later cannot quietly skip it.</t>
@@ -5819,7 +6541,7 @@
 Reason, which is the useful part. The materialised version broke a headline claim and did so silently. Granting a portfolio inserted a row in sec.user_portfolio and no matching grant, so the new entitlement did *nothing* until the next rebuild -- while the entitlement tables said it should. That is precisely the failure a single access model is supposed to remove: two descriptions of who may see what, drifting apart between runs. test_onboarding_a_user_and_a_portfolio_is_pure_insert caught it, which is the argument for having written that test as an assertion about behaviour rather than about rows.</t>
         </is>
       </c>
-      <c r="E31" s="14" t="inlineStr">
+      <c r="E31" s="15" t="inlineStr">
         <is>
           <t>Not recorded as a separate reason in DECISIONS.md; see the choice.</t>
         </is>
@@ -5830,8 +6552,74 @@
         </is>
       </c>
     </row>
+    <row r="32" ht="154" customHeight="1">
+      <c r="A32" s="8" t="inlineStr">
+        <is>
+          <t>D028</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>The closing posting of a day is the end of its running-balance chain</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>(a) Keep the highest-id tie-break. (b) Use file order. (c) Take the end of the balance chain, and use a documented fallback only where the chain does not resolve, marking those rows. (d) Report NULL where ambiguous.</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>(c), with the lowest trans_id among the chain ends as the fallback and closing_basis ('single posting' / 'balance chain' / 'ambiguous') on every month-end row.</t>
+        </is>
+      </c>
+      <c r="E32" s="15" t="inlineStr">
+        <is>
+          <t>It implements A14 ("the balance after the last posting") with the only evidence of order the source holds, instead of a proxy that is wrong 99.6% of the time. (d) would silently shrink Q9's population; (a) and (b) fabricate an order. The fallback is a measured heuristic, not a claim of chronology, so the 1.2% of account-months it decides stay visibly marked.</t>
+        </is>
+      </c>
+      <c r="F32" s="11" t="inlineStr">
+        <is>
+          <t>Q9 moves from 43,808.94 to 43,810.47. The same correction applies to the two reconciliation rules, which read the "last reported balance" the same way: material breaks fall from 55 to 14 and the rounding band from 81 to 70, because 52 of the old flags were a mid-day balance read as the final one. The data owner should confirm the fallback for the 2,303 ambiguous account-months.
+tests/test_month_end.py runs the production SQL block against synthetic postings (same-day chains, gaps, first and last months, ambiguity) and checks the real table against an independent derivation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="280" customHeight="1">
+      <c r="A33" s="8" t="inlineStr">
+        <is>
+          <t>D029</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>Generated SQL must match a declared intent before it runs</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>(a) More prompt text. (b) EXPLAIN the query before running it. (c) Make the model state its intent as a small intermediate representation (IR) and verify the SQL against the IR, the semantic layer and the database before execution. (d) Compile SQL from the IR and drop model SQL entirely.</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>(c), with (b) as part of it: the IR is checked against the certified metrics, every column the SQL references is resolved against the semantic layer, the period filter is evaluated day by day against the IR's half-open ranges, joins must be declared and must not fan out the counted entity, required grouping and filters must be present, and PostgreSQL plans the query (EXPLAIN) before it executes. After execution, a certified metric is recomputed from the IR alone and must agree before the answer is shown. Anything missing, malformed or unverifiable fails with the reason.</t>
+        </is>
+      </c>
+      <c r="E33" s="15" t="inlineStr">
+        <is>
+          <t>(a) is advice, not a control. (d) is the long-term target for certified metrics but removes the model from questions it handles well today. (c) catches every failure class seen so far while keeping the model's SQL.</t>
+        </is>
+      </c>
+      <c r="F33" s="11" t="inlineStr">
+        <is>
+          <t>Questions outside the certified metrics are refused rather than answered unverified, and some correct but unusual SQL is rejected and retried. One metric per answer: a second measure in the same SELECT runs but is not verified. A verified answer proves the SQL computes the declared intent with the certified definitions; whether the intent is what the user meant is shown, not proven, which is why the IR is reported beside the answer.
+src/sql_ir.py is the only verifier. The question runner and the web app reach it through one function, run_questions.verify_and_execute: guard, IR, columns, consistency, then (only then) the two-factor login, EXPLAIN, guarded execution and recomputation on the caller's own RLS-bound connection. A refusal records the stage and the reason, keeps the SQL, returns no rows, and is fed back for the single retry. Only a fully verified answer is recorded as answered and evaluated. tests/test_sql_ir.py covers the observed failure, quarters, date columns, fan-out, grouping, malformed IRs and both application paths with a scripted model; the brief's ten recorded answers still verify.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:F31"/>
+  <autoFilter ref="A4:F33"/>
   <mergeCells count="1">
     <mergeCell ref="A2:F2"/>
   </mergeCells>
